--- a/table/theory_eval_refined_coding_refined.xlsx
+++ b/table/theory_eval_refined_coding_refined.xlsx
@@ -1,26 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/71577d21dfa8bb45/research/projects/Rethinking_Evaluation/codex/outputs/audits/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{AD76AC79-7052-5D44-995B-DB61B37DE43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5777EC6E-E323-7B4A-A15D-06EEC6F17F3B}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="13720" yWindow="-26320" windowWidth="36680" windowHeight="23040" xr2:uid="{01BF8AE9-CFEC-5046-A9FC-F7460E71BFF9}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="theory_eval_refined_coding" sheetId="1" r:id="rId1"/>
+    <sheet name="theory_eval_refined_coding" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="646">
   <si>
     <t>Paper_ID</t>
   </si>
@@ -88,8 +84,7 @@
     <t>Xiao2024HealMe</t>
   </si>
   <si>
-    <t>HealMe: Harnessing Cognitive Reframing in Large Language Models for
-Psychotherapy_x000D_</t>
+    <t xml:space="preserve">HealMe: Harnessing Cognitive Reframing in Large Language Models for Psychotherapy</t>
   </si>
   <si>
     <t>./papers/1.pdf</t>
@@ -98,34 +93,34 @@
     <t>Strong</t>
   </si>
   <si>
-    <t>CBT; cognitive reframing; therapist competence; CBT adherence; ACCS</t>
-  </si>
-  <si>
-    <t>CBT/cognitive reframing shapes the task and dataset; scoring draws on established CBT therapist competence/adherence instruments.</t>
-  </si>
-  <si>
-    <t>pp.1, 3, 5</t>
-  </si>
-  <si>
-    <t>Evaluation criteria draw from established measures for therapist competence and adherence to core CBT principles, with expert ratings of empathy, guidance, and logical coherence.</t>
-  </si>
-  <si>
-    <t>p.5 Scoring Criteria</t>
-  </si>
-  <si>
-    <t>Validated scale; Established therapy/counseling coding system; Theory-specific rubric; Custom expert rating</t>
+    <t xml:space="preserve">CBT; cognitive reframing; therapist competence; CBT adherence; ACCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT/cognitive reframing shapes the task and dataset; scoring draws on established CBT therapist competence/adherence instruments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 3, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation criteria draw from established measures for therapist competence and adherence to core CBT principles, with expert ratings of empathy, guidance, and logical coherence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5 Scoring Criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; Established therapy/counseling coding system; Theory-specific rubric; Custom expert rating</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>No downstream human learning, clinical, safety, or deployment consequence is measured.</t>
-  </si>
-  <si>
-    <t>Evaluation/Results sections</t>
-  </si>
-  <si>
-    <t>Formal CBT-related competence/adherence criteria define evaluation, but outcomes remain model-output level.</t>
+    <t xml:space="preserve">No downstream human learning, clinical, safety, or deployment consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation/Results sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formal CBT-related competence/adherence criteria define evaluation, but outcomes remain model-output level.</t>
   </si>
   <si>
     <t>High</t>
@@ -134,85 +129,85 @@
     <t>No</t>
   </si>
   <si>
-    <t>Use refined Theory_Grounding and Theory_Operationalized_In_Evaluation labels; add Theory_Eval_Type and Theory_Eval_Consequence_Level columns.</t>
-  </si>
-  <si>
-    <t>Refined PDF-based theory/evaluation coding; input files not modified.</t>
+    <t xml:space="preserve">Use refined Theory_Grounding and Theory_Operationalized_In_Evaluation labels; add Theory_Eval_Type and Theory_Eval_Consequence_Level columns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refined PDF-based theory/evaluation coding; input files not modified.</t>
   </si>
   <si>
     <t>Gabriel2024Can</t>
   </si>
   <si>
-    <t>Can AI Relate: Testing Large Language Model Response for Mental Health Support</t>
+    <t xml:space="preserve">Can AI Relate: Testing Large Language Model Response for Mental Health Support</t>
   </si>
   <si>
     <t>./papers/6.pdf</t>
   </si>
   <si>
-    <t>motivational interviewing; empathy; quality-of-care metrics</t>
-  </si>
-  <si>
-    <t>The paper frames LLM mental-health support around equity in empathy and adherence to motivational interviewing theory.</t>
-  </si>
-  <si>
-    <t>p.1 Abstract/Introduction</t>
-  </si>
-  <si>
-    <t>motivational interviewing adherence; empathy; quality-of-care metrics</t>
-  </si>
-  <si>
-    <t>Clinician and automatic evaluations measure equity in empathy and adherence of LLM responses to motivational interviewing theory.</t>
-  </si>
-  <si>
-    <t>Theory-specific rubric; Custom expert rating</t>
-  </si>
-  <si>
-    <t>No downstream human learning, clinical outcome, or deployment consequence is measured.</t>
-  </si>
-  <si>
-    <t>MI adherence and empathy are explicit construct-specific evaluation dimensions.</t>
+    <t xml:space="preserve">motivational interviewing; empathy; quality-of-care metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper frames LLM mental-health support around equity in empathy and adherence to motivational interviewing theory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.1 Abstract/Introduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">motivational interviewing adherence; empathy; quality-of-care metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinician and automatic evaluations measure equity in empathy and adherence of LLM responses to motivational interviewing theory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-specific rubric; Custom expert rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream human learning, clinical outcome, or deployment consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI adherence and empathy are explicit construct-specific evaluation dimensions.</t>
   </si>
   <si>
     <t>Haydarov2025Towards</t>
   </si>
   <si>
-    <t>Towards AI-Assisted Psychotherapy: Emotion-Guided Generative Interventions</t>
+    <t xml:space="preserve">Towards AI-Assisted Psychotherapy: Emotion-Guided Generative Interventions</t>
   </si>
   <si>
     <t>./papers/10.pdf</t>
   </si>
   <si>
-    <t>Ekman discrete emotion framework; Russell valence-arousal model; emotional labor; empathy; valence/arousal</t>
-  </si>
-  <si>
-    <t>Emotion representation frameworks and emotional dissonance motivate multimodal emotion-guided intervention design.</t>
-  </si>
-  <si>
-    <t>pp.3, 5-6</t>
+    <t xml:space="preserve">Ekman discrete emotion framework; Russell valence-arousal model; emotional labor; empathy; valence/arousal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emotion representation frameworks and emotional dissonance motivate multimodal emotion-guided intervention design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.3, 5-6</t>
   </si>
   <si>
     <t>Partial</t>
   </si>
   <si>
-    <t>empathy; comprehensiveness; applicability; valence/arousal; emotional dissonance</t>
-  </si>
-  <si>
-    <t>Expert ratings include empathy, comprehensiveness, and applicability; valence/arousal estimates are used for emotion-aware prompting and analysis, but the evaluation rubric is custom rather than a validated therapy-process scale.</t>
-  </si>
-  <si>
-    <t>pp.7, 16-17 Human/expert evaluation figures</t>
-  </si>
-  <si>
-    <t>Custom expert rating; Affective/emotional dynamics metric</t>
-  </si>
-  <si>
-    <t>No downstream therapeutic, learning, safety, or deployment consequence is measured.</t>
-  </si>
-  <si>
-    <t>Evaluation/Limitations sections</t>
-  </si>
-  <si>
-    <t>Emotion theory is central to design, but evaluation depth is mostly custom expert assessment.</t>
+    <t xml:space="preserve">empathy; comprehensiveness; applicability; valence/arousal; emotional dissonance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expert ratings include empathy, comprehensiveness, and applicability; valence/arousal estimates are used for emotion-aware prompting and analysis, but the evaluation rubric is custom rather than a validated therapy-process scale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.7, 16-17 Human/expert evaluation figures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom expert rating; Affective/emotional dynamics metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream therapeutic, learning, safety, or deployment consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation/Limitations sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emotion theory is central to design, but evaluation depth is mostly custom expert assessment.</t>
   </si>
   <si>
     <t>Medium</t>
@@ -224,862 +219,862 @@
     <t>Qiu2025EmoAgent</t>
   </si>
   <si>
-    <t>EmoAgent: Assessing and Safeguarding Human-AI Interaction for Mental Health Safety</t>
+    <t xml:space="preserve">EmoAgent: Assessing and Safeguarding Human-AI Interaction for Mental Health Safety</t>
   </si>
   <si>
     <t>./papers/13.pdf</t>
   </si>
   <si>
-    <t>Beck cognitive models; PHQ-9; PDI; PANSS; depression; psychosis; delusion; mental-health safety</t>
-  </si>
-  <si>
-    <t>Virtual users integrate cognitive models for depression, psychosis, and delusion, and the system is framed around mental-health safety.</t>
-  </si>
-  <si>
-    <t>p.2 Method overview</t>
-  </si>
-  <si>
-    <t>PHQ-9; PDI; PANSS; depression; delusion; psychosis; safety deterioration rate</t>
-  </si>
-  <si>
-    <t>EmoEval measures simulated users with clinically validated PHQ-9, PDI, and PANSS tools and tracks mental-state deterioration/safeguard effects.</t>
-  </si>
-  <si>
-    <t>p.2; p.9 Results/Limitations</t>
-  </si>
-  <si>
-    <t>Validated scale; Clinical diagnostic benchmark; Theory-specific benchmark/task; Theory-specific rubric</t>
-  </si>
-  <si>
-    <t>Safety/deployment consequence</t>
-  </si>
-  <si>
-    <t>The evaluation measures simulated mental-health deterioration and safeguard intervention effects, framed as safety consequences for conversational AI.</t>
-  </si>
-  <si>
-    <t>p.2; p.9</t>
-  </si>
-  <si>
-    <t>Validated clinical instruments and safety outcomes define evaluation.</t>
+    <t xml:space="preserve">Beck cognitive models; PHQ-9; PDI; PANSS; depression; psychosis; delusion; mental-health safety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtual users integrate cognitive models for depression, psychosis, and delusion, and the system is framed around mental-health safety.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.2 Method overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHQ-9; PDI; PANSS; depression; delusion; psychosis; safety deterioration rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmoEval measures simulated users with clinically validated PHQ-9, PDI, and PANSS tools and tracks mental-state deterioration/safeguard effects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.2; p.9 Results/Limitations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; Clinical diagnostic benchmark; Theory-specific benchmark/task; Theory-specific rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety/deployment consequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The evaluation measures simulated mental-health deterioration and safeguard intervention effects, framed as safety consequences for conversational AI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.2; p.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated clinical instruments and safety outcomes define evaluation.</t>
   </si>
   <si>
     <t>Aghakhani2025From</t>
   </si>
   <si>
-    <t>From Conversation to Automation: Leveraging LLMs for Problem-Solving Therapy Analysis</t>
+    <t xml:space="preserve">From Conversation to Automation: Leveraging LLMs for Problem-Solving Therapy Analysis</t>
   </si>
   <si>
     <t>./papers/15.pdf</t>
   </si>
   <si>
-    <t>Problem-Solving Therapy; PST strategies; therapeutic alliance; autonomy</t>
-  </si>
-  <si>
-    <t>Problem-Solving Therapy strategies and therapeutic alliance/autonomy constructs shape the annotation/analysis of therapeutic dialogue.</t>
-  </si>
-  <si>
-    <t>pp.4, 9</t>
-  </si>
-  <si>
-    <t>PST strategies; therapeutic alliance; autonomy; therapeutic dialogue annotation</t>
-  </si>
-  <si>
-    <t>The evaluation/analysis assesses whether AI-assisted therapy implements PST strategies and maintains therapeutic alliances through annotated therapeutic dialogues.</t>
-  </si>
-  <si>
-    <t>p.9 Conclusion/Evaluation framework discussion</t>
-  </si>
-  <si>
-    <t>Theory-specific benchmark/task; Theory-specific rubric; LLM judge with theory-specific criteria</t>
-  </si>
-  <si>
-    <t>The paper evaluates annotation/model performance rather than downstream human or therapeutic consequences.</t>
-  </si>
-  <si>
-    <t>Evaluation/Conclusion sections</t>
-  </si>
-  <si>
-    <t>PST and alliance are construct-specific evaluation/annotation targets, though details merit manual verification.</t>
+    <t xml:space="preserve">Problem-Solving Therapy; PST strategies; therapeutic alliance; autonomy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problem-Solving Therapy strategies and therapeutic alliance/autonomy constructs shape the annotation/analysis of therapeutic dialogue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.4, 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PST strategies; therapeutic alliance; autonomy; therapeutic dialogue annotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The evaluation/analysis assesses whether AI-assisted therapy implements PST strategies and maintains therapeutic alliances through annotated therapeutic dialogues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.9 Conclusion/Evaluation framework discussion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-specific benchmark/task; Theory-specific rubric; LLM judge with theory-specific criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper evaluates annotation/model performance rather than downstream human or therapeutic consequences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation/Conclusion sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PST and alliance are construct-specific evaluation/annotation targets, though details merit manual verification.</t>
   </si>
   <si>
     <t>Wang2025AnnaAgent</t>
   </si>
   <si>
-    <t>AnnaAgent: Dynamic Evolution Agent System with Multi-Session Memory for Realistic Seeker Simulation</t>
+    <t xml:space="preserve">AnnaAgent: Dynamic Evolution Agent System with Multi-Session Memory for Realistic Seeker Simulation</t>
   </si>
   <si>
     <t>./papers/18.pdf</t>
   </si>
   <si>
-    <t>self-report scales; Beck scale; Social Adaptation Self-evaluation Scale; CBT triggering events; psychological status</t>
-  </si>
-  <si>
-    <t>Validated scales and CBT triggering events inform simulated seeker state, but the theory link is mainly for simulation design.</t>
-  </si>
-  <si>
-    <t>p.6 Method; references p.10</t>
-  </si>
-  <si>
-    <t>None found</t>
-  </si>
-  <si>
-    <t>Checked evaluation sections did not show the self-report scales or CBT constructs used as evaluation criteria; evaluation focuses on simulation quality/realism.</t>
-  </si>
-  <si>
-    <t>Evaluation/Results sections checked</t>
-  </si>
-  <si>
-    <t>Generic quality metric only</t>
-  </si>
-  <si>
-    <t>No consequence-level theory-based evaluation found.</t>
-  </si>
-  <si>
-    <t>Theory-related constructs shape state design, not evaluation.</t>
+    <t xml:space="preserve">self-report scales; Beck scale; Social Adaptation Self-evaluation Scale; CBT triggering events; psychological status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scales and CBT triggering events inform simulated seeker state, but the theory link is mainly for simulation design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.6 Method; references p.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked evaluation sections did not show the self-report scales or CBT constructs used as evaluation criteria; evaluation focuses on simulation quality/realism.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation/Results sections checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic quality metric only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No consequence-level theory-based evaluation found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-related constructs shape state design, not evaluation.</t>
   </si>
   <si>
     <t>Wang2025CARE-Bench</t>
   </si>
   <si>
-    <t>CARE-Bench: A Benchmark of Diverse Client Simulations Guided by Expert Principles for Evaluating LLMs in Psychological Counseling</t>
+    <t xml:space="preserve">CARE-Bench: A Benchmark of Diverse Client Simulations Guided by Expert Principles for Evaluating LLMs in Psychological Counseling</t>
   </si>
   <si>
     <t>./papers/21.pdf</t>
   </si>
   <si>
-    <t>counseling competence; expert-guided principles; Counseling Competencies Scale</t>
-  </si>
-  <si>
-    <t>The benchmark is motivated by counseling competence and expert principles for client simulations.</t>
-  </si>
-  <si>
-    <t>pp.2, 5, 8</t>
-  </si>
-  <si>
-    <t>counseling competence; authenticity; training readiness; expert-guided principles</t>
-  </si>
-  <si>
-    <t>Evaluation uses multidimensional counselor/client-simulation criteria, including authenticity, challenge, training readiness, and counseling competence.</t>
-  </si>
-  <si>
-    <t>p.5 Table 2; p.5 Multidimensional Scale Evaluation</t>
-  </si>
-  <si>
-    <t>Theory-specific benchmark/task; Theory-specific rubric; Custom expert rating</t>
-  </si>
-  <si>
-    <t>No measured trainee learning or client outcome; evaluation is benchmark/simulation quality.</t>
-  </si>
-  <si>
-    <t>Counseling competence is a clear construct-specific benchmark/evaluation target.</t>
+    <t xml:space="preserve">counseling competence; expert-guided principles; Counseling Competencies Scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The benchmark is motivated by counseling competence and expert principles for client simulations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 5, 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">counseling competence; authenticity; training readiness; expert-guided principles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses multidimensional counselor/client-simulation criteria, including authenticity, challenge, training readiness, and counseling competence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5 Table 2; p.5 Multidimensional Scale Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-specific benchmark/task; Theory-specific rubric; Custom expert rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No measured trainee learning or client outcome; evaluation is benchmark/simulation quality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counseling competence is a clear construct-specific benchmark/evaluation target.</t>
   </si>
   <si>
     <t>Sungarda2025GenAI</t>
   </si>
   <si>
-    <t>GenAI for Social Work Field Education: Client Simulation with Real-Time Feedback</t>
+    <t xml:space="preserve">GenAI for Social Work Field Education: Client Simulation with Real-Time Feedback</t>
   </si>
   <si>
     <t>./papers/23.pdf</t>
   </si>
   <si>
-    <t>motivational interviewing; MI stages; CBT-based cognitive modeling; counseling skill classification</t>
-  </si>
-  <si>
-    <t>The training system integrates MI framework/stages and counseling-skill classification for social-work field education.</t>
-  </si>
-  <si>
-    <t>pp.2-3 Method</t>
-  </si>
-  <si>
-    <t>MI stages; counseling skill classification; stage-specific goals; trainee feedback</t>
-  </si>
-  <si>
-    <t>Evaluation/feedback checks MI stage progression and counseling-skill categories, including whether stage-specific goals are fulfilled.</t>
-  </si>
-  <si>
-    <t>pp.2-3 System design/evaluation workflow</t>
-  </si>
-  <si>
-    <t>No direct evidence of measured trainee learning or skill acquisition outcomes.</t>
-  </si>
-  <si>
-    <t>Evaluation/User study sections checked</t>
-  </si>
-  <si>
-    <t>MI stages and counseling skills define what is assessed, but outcome-level learning is not measured.</t>
+    <t xml:space="preserve">motivational interviewing; MI stages; CBT-based cognitive modeling; counseling skill classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The training system integrates MI framework/stages and counseling-skill classification for social-work field education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2-3 Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI stages; counseling skill classification; stage-specific goals; trainee feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation/feedback checks MI stage progression and counseling-skill categories, including whether stage-specific goals are fulfilled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2-3 System design/evaluation workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No direct evidence of measured trainee learning or skill acquisition outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation/User study sections checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI stages and counseling skills define what is assessed, but outcome-level learning is not measured.</t>
   </si>
   <si>
     <t>Liu2023ChatCounselor</t>
   </si>
   <si>
-    <t>ChatCounselor: A Large Language Models for Mental Health Support</t>
+    <t xml:space="preserve">ChatCounselor: A Large Language Models for Mental Health Support</t>
   </si>
   <si>
     <t>./papers/29.pdf</t>
   </si>
   <si>
-    <t>emotional support; counseling strategies; Counseling Bench</t>
-  </si>
-  <si>
-    <t>The paper uses common psychological counseling strategies and emotional support constructs, without a deeply specified formal theory.</t>
-  </si>
-  <si>
-    <t>p.4 Counseling Bench</t>
-  </si>
-  <si>
-    <t>counseling strategies; emotional support; information; direct guidance; GPT-4 referee criteria</t>
-  </si>
-  <si>
-    <t>GPT-4 judge prompts assess whether responses use specified counseling strategies and align with natural counseling tone, but the strategy framework is custom/informal.</t>
-  </si>
-  <si>
-    <t>p.4 Counseling Bench/Evaluation</t>
-  </si>
-  <si>
-    <t>LLM judge with theory-specific criteria; Theory-specific rubric</t>
-  </si>
-  <si>
-    <t>No downstream human learning, clinical outcome, or safety consequence is measured.</t>
-  </si>
-  <si>
-    <t>Evaluation sections</t>
-  </si>
-  <si>
-    <t>Evaluation uses theory-relevant strategy criteria, but the framework is broad and custom.</t>
+    <t xml:space="preserve">emotional support; counseling strategies; Counseling Bench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper uses common psychological counseling strategies and emotional support constructs, without a deeply specified formal theory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.4 Counseling Bench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">counseling strategies; emotional support; information; direct guidance; GPT-4 referee criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-4 judge prompts assess whether responses use specified counseling strategies and align with natural counseling tone, but the strategy framework is custom/informal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.4 Counseling Bench/Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM judge with theory-specific criteria; Theory-specific rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream human learning, clinical outcome, or safety consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses theory-relevant strategy criteria, but the framework is broad and custom.</t>
   </si>
   <si>
     <t>Chiu2024A</t>
   </si>
   <si>
-    <t>A Computational Framework for Behavioral Assessment of LLM Therapists</t>
+    <t xml:space="preserve">A Computational Framework for Behavioral Assessment of LLM Therapists</t>
   </si>
   <si>
     <t>./papers/31.pdf</t>
   </si>
   <si>
-    <t>CBT; motivational interviewing; psychotherapy intervention quality; patient outcomes</t>
-  </si>
-  <si>
-    <t>The framework is motivated by evidence-based therapeutic interventions and psychotherapy quality assessment.</t>
-  </si>
-  <si>
-    <t>pp.2, 20</t>
-  </si>
-  <si>
-    <t>psychotherapy behavior labels; high/low quality labels; intervention quality; patient outcomes</t>
-  </si>
-  <si>
-    <t>Automated behavioral assessment uses high/low-quality psychotherapy labels from a prior study and behavioral measures relevant to therapeutic intervention quality.</t>
-  </si>
-  <si>
-    <t>p.20 Limitations/Assessment description</t>
-  </si>
-  <si>
-    <t>Theory-specific benchmark/task; Theory-specific rubric</t>
-  </si>
-  <si>
-    <t>Patient outcomes are discussed as a possible quality definition, but not directly measured in this study.</t>
-  </si>
-  <si>
-    <t>p.20 Limitations</t>
-  </si>
-  <si>
-    <t>Therapy-quality labels and behavioral metrics define evaluation, though provenance should be checked.</t>
+    <t xml:space="preserve">CBT; motivational interviewing; psychotherapy intervention quality; patient outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The framework is motivated by evidence-based therapeutic interventions and psychotherapy quality assessment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psychotherapy behavior labels; high/low quality labels; intervention quality; patient outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated behavioral assessment uses high/low-quality psychotherapy labels from a prior study and behavioral measures relevant to therapeutic intervention quality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.20 Limitations/Assessment description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-specific benchmark/task; Theory-specific rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient outcomes are discussed as a possible quality definition, but not directly measured in this study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.20 Limitations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapy-quality labels and behavioral metrics define evaluation, though provenance should be checked.</t>
   </si>
   <si>
     <t>Li2024Understanding</t>
   </si>
   <si>
-    <t>Understanding the Therapeutic Relationship between Counselors and Clients in Online Text-based Counseling using LLMs</t>
+    <t xml:space="preserve">Understanding the Therapeutic Relationship between Counselors and Clients in Online Text-based Counseling using LLMs</t>
   </si>
   <si>
     <t>./papers/34.pdf</t>
   </si>
   <si>
-    <t>therapeutic alliance; working alliance; alliance scales; counseling outcomes</t>
-  </si>
-  <si>
-    <t>A theoretically grounded therapeutic-alliance framework is adapted for online text counseling.</t>
-  </si>
-  <si>
-    <t>pp.1-3 Framework and Guidelines</t>
-  </si>
-  <si>
-    <t>therapeutic alliance; working alliance; alliance scales; expert guidelines; counseling outcomes</t>
-  </si>
-  <si>
-    <t>Expert and LLM evaluations measure therapeutic alliance using adapted alliance definitions/scales and relate alliance to favorable counseling outcomes.</t>
-  </si>
-  <si>
-    <t>pp.1-3; p.2 outcome analysis</t>
-  </si>
-  <si>
-    <t>Validated scale; Theory-specific rubric; LLM judge with theory-specific criteria</t>
-  </si>
-  <si>
-    <t>Clinical/therapeutic outcome</t>
-  </si>
-  <si>
-    <t>The paper analyzes association between therapeutic alliance and favorable counseling outcomes in counseling sessions.</t>
-  </si>
-  <si>
-    <t>p.2 Introduction/Findings</t>
-  </si>
-  <si>
-    <t>Alliance is both the grounding framework and the evaluated construct, with outcome association.</t>
+    <t xml:space="preserve">therapeutic alliance; working alliance; alliance scales; counseling outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A theoretically grounded therapeutic-alliance framework is adapted for online text counseling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1-3 Framework and Guidelines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">therapeutic alliance; working alliance; alliance scales; expert guidelines; counseling outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expert and LLM evaluations measure therapeutic alliance using adapted alliance definitions/scales and relate alliance to favorable counseling outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1-3; p.2 outcome analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; Theory-specific rubric; LLM judge with theory-specific criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical/therapeutic outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper analyzes association between therapeutic alliance and favorable counseling outcomes in counseling sessions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.2 Introduction/Findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alliance is both the grounding framework and the evaluated construct, with outcome association.</t>
   </si>
   <si>
     <t>Wang2024Towards</t>
   </si>
   <si>
-    <t>Towards a Client-Centered Assessment of LLM Therapists by Client Simulation</t>
+    <t xml:space="preserve">Towards a Client-Centered Assessment of LLM Therapists by Client Simulation</t>
   </si>
   <si>
     <t>./papers/38.pdf</t>
   </si>
   <si>
-    <t>therapeutic alliance; session outcome; self-reported feelings; client-centered assessment</t>
-  </si>
-  <si>
-    <t>The paper frames evaluation around client-centered constructs such as alliance, outcomes, and self-reported feelings.</t>
-  </si>
-  <si>
-    <t>pp.2, 6</t>
-  </si>
-  <si>
-    <t>session outcome; therapeutic alliance; self-reported feelings; client questionnaires</t>
-  </si>
-  <si>
-    <t>Simulated clients complete questionnaires to assess session outcome, therapeutic alliance, and self-reported feelings.</t>
-  </si>
-  <si>
-    <t>p.2 Figure/overview; p.6 Results</t>
-  </si>
-  <si>
-    <t>Validated scale; HCI/perception construct scale; Theory-specific rubric</t>
-  </si>
-  <si>
-    <t>Simulated outcome</t>
-  </si>
-  <si>
-    <t>Outcome and alliance measures are produced through simulated clients rather than real clients.</t>
-  </si>
-  <si>
-    <t>p.2; p.6</t>
-  </si>
-  <si>
-    <t>Evaluation is construct-specific but consequence evidence is simulated.</t>
+    <t xml:space="preserve">therapeutic alliance; session outcome; self-reported feelings; client-centered assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper frames evaluation around client-centered constructs such as alliance, outcomes, and self-reported feelings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">session outcome; therapeutic alliance; self-reported feelings; client questionnaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulated clients complete questionnaires to assess session outcome, therapeutic alliance, and self-reported feelings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.2 Figure/overview; p.6 Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; HCI/perception construct scale; Theory-specific rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulated outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome and alliance measures are produced through simulated clients rather than real clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.2; p.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation is construct-specific but consequence evidence is simulated.</t>
   </si>
   <si>
     <t>Hu2024PsycoLLM</t>
   </si>
   <si>
-    <t>PsycoLLM: Enhancing LLM for Psychological Understanding and Evaluation</t>
+    <t xml:space="preserve">PsycoLLM: Enhancing LLM for Psychological Understanding and Evaluation</t>
   </si>
   <si>
     <t>./papers/39.pdf</t>
   </si>
   <si>
-    <t>psychological counseling examination; psychological theory; professional ethics; cognitive errors</t>
-  </si>
-  <si>
-    <t>The work is grounded in psychology/counseling examination knowledge and professional ethics, but not a specific therapeutic framework.</t>
-  </si>
-  <si>
-    <t>pp.2, 7, 9-10</t>
-  </si>
-  <si>
-    <t>psychological counseling exam questions; case-based diagnosis; cognitive errors; professional ethics</t>
-  </si>
-  <si>
-    <t>Benchmark tasks use psychology/counseling examination questions and case-based QA, while metrics are mainly MCQ accuracy and generic ROUGE/BLEU/BERTScore.</t>
-  </si>
-  <si>
-    <t>pp.7, 9 Evaluation/Results</t>
-  </si>
-  <si>
-    <t>Clinical diagnostic benchmark; Theory-specific benchmark/task; Generic quality metric only</t>
-  </si>
-  <si>
-    <t>No consequence-level evaluation found.</t>
-  </si>
-  <si>
-    <t>Psychology-domain tasks are theory-relevant, but metric depth is mostly generic.</t>
+    <t xml:space="preserve">psychological counseling examination; psychological theory; professional ethics; cognitive errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The work is grounded in psychology/counseling examination knowledge and professional ethics, but not a specific therapeutic framework.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 7, 9-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psychological counseling exam questions; case-based diagnosis; cognitive errors; professional ethics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benchmark tasks use psychology/counseling examination questions and case-based QA, while metrics are mainly MCQ accuracy and generic ROUGE/BLEU/BERTScore.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.7, 9 Evaluation/Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical diagnostic benchmark; Theory-specific benchmark/task; Generic quality metric only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No consequence-level evaluation found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychology-domain tasks are theory-relevant, but metric depth is mostly generic.</t>
   </si>
   <si>
     <t>Fouda2026PsychiatryBench</t>
   </si>
   <si>
-    <t>PsychiatryBench: a multi-task benchmark for LLMs in psychiatry</t>
+    <t xml:space="preserve">PsychiatryBench: a multi-task benchmark for LLMs in psychiatry</t>
   </si>
   <si>
     <t>./papers/45.pdf</t>
   </si>
   <si>
-    <t>DSM-5; ICD-10; NICE guidelines; APA guidelines; psychiatry clinical reasoning</t>
-  </si>
-  <si>
-    <t>PsychiatryBench is structured around standardized diagnostic frameworks and clinical practice guidelines.</t>
-  </si>
-  <si>
-    <t>p.8 Methodology</t>
-  </si>
-  <si>
-    <t>DSM-5; ICD-10; NICE; APA; clinical relevance; psychiatric reasoning rubric</t>
-  </si>
-  <si>
-    <t>The benchmark and LLM-as-judge rubric score psychiatric answer quality across clinical dimensions such as accuracy, completeness, and clinical relevance.</t>
-  </si>
-  <si>
-    <t>pp.8, 12 Evaluation/Rubric</t>
-  </si>
-  <si>
-    <t>Clinical diagnostic benchmark; Theory-specific benchmark/task; Theory-specific rubric; LLM judge with theory-specific criteria</t>
-  </si>
-  <si>
-    <t>Evaluation is benchmark/model performance; no patient or deployment consequence is measured.</t>
-  </si>
-  <si>
-    <t>Clinical frameworks and structured clinical rubrics define evaluation.</t>
+    <t xml:space="preserve">DSM-5; ICD-10; NICE guidelines; APA guidelines; psychiatry clinical reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PsychiatryBench is structured around standardized diagnostic frameworks and clinical practice guidelines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.8 Methodology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSM-5; ICD-10; NICE; APA; clinical relevance; psychiatric reasoning rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The benchmark and LLM-as-judge rubric score psychiatric answer quality across clinical dimensions such as accuracy, completeness, and clinical relevance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.8, 12 Evaluation/Rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical diagnostic benchmark; Theory-specific benchmark/task; Theory-specific rubric; LLM judge with theory-specific criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation is benchmark/model performance; no patient or deployment consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical frameworks and structured clinical rubrics define evaluation.</t>
   </si>
   <si>
     <t>Cai2026Exploring</t>
   </si>
   <si>
-    <t>Exploring Safety Alignment Evaluation of LLMs in Chinese Mental Health Dialogues via LLM-as-Judge</t>
+    <t xml:space="preserve">Exploring Safety Alignment Evaluation of LLMs in Chinese Mental Health Dialogues via LLM-as-Judge</t>
   </si>
   <si>
     <t>./papers/47.pdf</t>
   </si>
   <si>
-    <t>WHO mhGAP; LIVE LIFE; psychological intervention principles; therapeutic alliance; emotion regulation; risk assessment</t>
-  </si>
-  <si>
-    <t>High-risk mental-health dialogue evaluation is grounded in crisis/intervention frameworks and psychological intervention principles.</t>
-  </si>
-  <si>
-    <t>pp.1, 12-13</t>
-  </si>
-  <si>
-    <t>WHO mhGAP; LIVE LIFE; safety taxonomy; empathy; therapeutic alliance; emotion regulation; risk assessment</t>
-  </si>
-  <si>
-    <t>LLM-as-judge criteria and annotation guidelines include empathy/collaboration, therapeutic alliance, evidence-based emotion regulation, exploration, and crisis/safety criteria.</t>
-  </si>
-  <si>
-    <t>pp.12-13 Evaluation criteria/Annotation guidelines</t>
-  </si>
-  <si>
-    <t>Theory-specific rubric; LLM judge with theory-specific criteria; Clinical diagnostic benchmark</t>
-  </si>
-  <si>
-    <t>Evaluation targets high-risk dialogue safety alignment, risk assessment, and crisis handling.</t>
-  </si>
-  <si>
-    <t>Safety and crisis-intervention constructs define evaluation and deployment-relevant consequences.</t>
+    <t xml:space="preserve">WHO mhGAP; LIVE LIFE; psychological intervention principles; therapeutic alliance; emotion regulation; risk assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-risk mental-health dialogue evaluation is grounded in crisis/intervention frameworks and psychological intervention principles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 12-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHO mhGAP; LIVE LIFE; safety taxonomy; empathy; therapeutic alliance; emotion regulation; risk assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM-as-judge criteria and annotation guidelines include empathy/collaboration, therapeutic alliance, evidence-based emotion regulation, exploration, and crisis/safety criteria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.12-13 Evaluation criteria/Annotation guidelines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-specific rubric; LLM judge with theory-specific criteria; Clinical diagnostic benchmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation targets high-risk dialogue safety alignment, risk assessment, and crisis handling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety and crisis-intervention constructs define evaluation and deployment-relevant consequences.</t>
   </si>
   <si>
     <t>Qiu2026PsyCLIENT</t>
   </si>
   <si>
-    <t>PsyCLIENT: Client Simulation via Conversational Trajectory Modeling for Trainee Practice and Model Evaluation in Mental Health Counseling</t>
+    <t xml:space="preserve">PsyCLIENT: Client Simulation via Conversational Trajectory Modeling for Trainee Practice and Model Evaluation in Mental Health Counseling</t>
   </si>
   <si>
     <t>./papers/49.pdf</t>
   </si>
   <si>
-    <t>client outcomes; process variables; counseling competence; listening; questioning; emotion-handling; technique practice</t>
-  </si>
-  <si>
-    <t>The paper uses counseling-process constructs for client simulation and counselor-evaluation framing, but without a strong named theory.</t>
-  </si>
-  <si>
-    <t>pp.1, 7, 23</t>
-  </si>
-  <si>
-    <t>listening; questioning; emotion-handling; technique-practice; authenticity; profile adherence</t>
-  </si>
-  <si>
-    <t>Expert counselors rate effectiveness dimensions such as listening, questioning, emotion-handling, technique practice, recommendation, and authenticity, but these are custom ratings.</t>
-  </si>
-  <si>
-    <t>pp.7-8; Appendix E.3</t>
-  </si>
-  <si>
-    <t>Custom expert rating; Theory-specific rubric</t>
-  </si>
-  <si>
-    <t>Training usefulness is expert-rated; no actual trainee learning or client outcome is measured.</t>
-  </si>
-  <si>
-    <t>Evaluation is theory-relevant but mainly custom expert ratings and simulation quality.</t>
+    <t xml:space="preserve">client outcomes; process variables; counseling competence; listening; questioning; emotion-handling; technique practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper uses counseling-process constructs for client simulation and counselor-evaluation framing, but without a strong named theory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 7, 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listening; questioning; emotion-handling; technique-practice; authenticity; profile adherence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expert counselors rate effectiveness dimensions such as listening, questioning, emotion-handling, technique practice, recommendation, and authenticity, but these are custom ratings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.7-8; Appendix E.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom expert rating; Theory-specific rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training usefulness is expert-rated; no actual trainee learning or client outcome is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation is theory-relevant but mainly custom expert ratings and simulation quality.</t>
   </si>
   <si>
     <t>Nguyen2025Do</t>
   </si>
   <si>
-    <t>Do Large Language Models Align with Core Mental Health Counseling Competencies?</t>
+    <t xml:space="preserve">Do Large Language Models Align with Core Mental Health Counseling Competencies?</t>
   </si>
   <si>
     <t>./papers/56.pdf</t>
   </si>
   <si>
-    <t>core mental-health counseling competencies; intervention techniques; clinical utility; counseling competence</t>
-  </si>
-  <si>
-    <t>The work is framed as evaluating alignment with core mental-health counseling competencies and intervention techniques.</t>
-  </si>
-  <si>
-    <t>p.3 Evaluation frameworks</t>
-  </si>
-  <si>
-    <t>counseling competencies; mental-health intervention techniques; clinical utility</t>
-  </si>
-  <si>
-    <t>The benchmark/evaluation framework assesses LLM alignment with counseling competencies across intervention techniques.</t>
-  </si>
-  <si>
-    <t>p.3 Evaluation frameworks; benchmark sections</t>
-  </si>
-  <si>
-    <t>No downstream human learning or therapeutic outcome measurement found.</t>
-  </si>
-  <si>
-    <t>Counseling competence defines the benchmark/evaluation target, but manual check is useful for exact rubric details.</t>
+    <t xml:space="preserve">core mental-health counseling competencies; intervention techniques; clinical utility; counseling competence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The work is framed as evaluating alignment with core mental-health counseling competencies and intervention techniques.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.3 Evaluation frameworks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">counseling competencies; mental-health intervention techniques; clinical utility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The benchmark/evaluation framework assesses LLM alignment with counseling competencies across intervention techniques.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.3 Evaluation frameworks; benchmark sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream human learning or therapeutic outcome measurement found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counseling competence defines the benchmark/evaluation target, but manual check is useful for exact rubric details.</t>
   </si>
   <si>
     <t>Zhang2025CBT-BENCH</t>
   </si>
   <si>
-    <t>CBT-BENCH: Evaluating Large Language Models on Assisting Cognitive Behavior Therapy</t>
+    <t xml:space="preserve">CBT-BENCH: Evaluating Large Language Models on Assisting Cognitive Behavior Therapy</t>
   </si>
   <si>
     <t>./papers/58.pdf</t>
   </si>
   <si>
-    <t>CBT; cognitive model; CTRS; therapeutic alliance rupture; CBT adherence/flexibility</t>
-  </si>
-  <si>
-    <t>CBT defines benchmark levels, cognitive-model understanding, and therapeutic response tasks.</t>
-  </si>
-  <si>
-    <t>pp.1, 5, 15</t>
-  </si>
-  <si>
-    <t>CBT; CTRS; therapeutic alliance rupture; CBT adherence; CBT competence</t>
-  </si>
-  <si>
-    <t>CBT-Bench evaluates CBT knowledge, cognitive model understanding, CBT assistance, adherence/flexibility, and alliance-rupture response criteria.</t>
-  </si>
-  <si>
-    <t>pp.1, 5, 15 criteria tables</t>
-  </si>
-  <si>
-    <t>Established therapy/counseling coding system; Theory-specific benchmark/task; Theory-specific rubric</t>
-  </si>
-  <si>
-    <t>Evaluation is model/benchmark performance rather than downstream human or clinical consequence.</t>
-  </si>
-  <si>
-    <t>CBT-specific tasks and criteria clearly define evaluation.</t>
+    <t xml:space="preserve">CBT; cognitive model; CTRS; therapeutic alliance rupture; CBT adherence/flexibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT defines benchmark levels, cognitive-model understanding, and therapeutic response tasks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 5, 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT; CTRS; therapeutic alliance rupture; CBT adherence; CBT competence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT-Bench evaluates CBT knowledge, cognitive model understanding, CBT assistance, adherence/flexibility, and alliance-rupture response criteria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 5, 15 criteria tables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Established therapy/counseling coding system; Theory-specific benchmark/task; Theory-specific rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation is model/benchmark performance rather than downstream human or clinical consequence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT-specific tasks and criteria clearly define evaluation.</t>
   </si>
   <si>
     <t>Kim2025KMI</t>
   </si>
   <si>
-    <t>KMI: A Dataset of Korean Motivational Interviewing Dialogues for Psychotherapy</t>
+    <t xml:space="preserve">KMI: A Dataset of Korean Motivational Interviewing Dialogues for Psychotherapy</t>
   </si>
   <si>
     <t>./papers/60.pdf</t>
   </si>
   <si>
-    <t>motivational interviewing; MI theory; therapeutic alliance</t>
-  </si>
-  <si>
-    <t>The KMI dataset and dialogue generation framework are explicitly grounded in motivational interviewing.</t>
-  </si>
-  <si>
-    <t>pp.1-2, 8</t>
-  </si>
-  <si>
-    <t>motivational interviewing; MI-derived metrics; MI dialogue quality</t>
-  </si>
-  <si>
-    <t>The paper proposes novel metrics derived from MI theory and uses expert evaluation of MI dialogues and the model trained on them.</t>
-  </si>
-  <si>
-    <t>pp.1-2; p.8 Discussion</t>
-  </si>
-  <si>
-    <t>No downstream client behavior change or therapy outcome is measured.</t>
-  </si>
-  <si>
-    <t>MI theory directly defines the dataset and evaluation metrics.</t>
+    <t xml:space="preserve">motivational interviewing; MI theory; therapeutic alliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The KMI dataset and dialogue generation framework are explicitly grounded in motivational interviewing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1-2, 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">motivational interviewing; MI-derived metrics; MI dialogue quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper proposes novel metrics derived from MI theory and uses expert evaluation of MI dialogues and the model trained on them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1-2; p.8 Discussion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream client behavior change or therapy outcome is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI theory directly defines the dataset and evaluation metrics.</t>
   </si>
   <si>
     <t>Deshpande2025Evaluating</t>
   </si>
   <si>
-    <t>Evaluating Large Language Models for Enhancing Live Chat Therapy: A Comparative Study with Psychotherapists</t>
+    <t xml:space="preserve">Evaluating Large Language Models for Enhancing Live Chat Therapy: A Comparative Study with Psychotherapists</t>
   </si>
   <si>
     <t>./papers/63.pdf</t>
   </si>
   <si>
-    <t>CBT; empathy; open-endedness; emotional support; therapeutic dialogue</t>
-  </si>
-  <si>
-    <t>CBT and therapist-behavior constructs appear in motivation/design, but the paper is primarily domain-grounded.</t>
-  </si>
-  <si>
-    <t>pp.1-2, 5</t>
-  </si>
-  <si>
-    <t>Checked evaluation uses BERTScore and therapist preference/appropriateness ratings without theory-specific criteria.</t>
-  </si>
-  <si>
-    <t>pp.6-8; p.12 user study example</t>
-  </si>
-  <si>
-    <t>No theory-related consequence-level evaluation found.</t>
-  </si>
-  <si>
-    <t>Prompt design is therapy-style inspired, but evaluation does not operationalize theory.</t>
+    <t xml:space="preserve">CBT; empathy; open-endedness; emotional support; therapeutic dialogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT and therapist-behavior constructs appear in motivation/design, but the paper is primarily domain-grounded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1-2, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked evaluation uses BERTScore and therapist preference/appropriateness ratings without theory-specific criteria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.6-8; p.12 user study example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No theory-related consequence-level evaluation found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prompt design is therapy-style inspired, but evaluation does not operationalize theory.</t>
   </si>
   <si>
     <t>Jaiswal2024Building</t>
   </si>
   <si>
-    <t>Building Personality-Adaptive Conversational AI for Mental Health Therapy</t>
+    <t xml:space="preserve">Building Personality-Adaptive Conversational AI for Mental Health Therapy</t>
   </si>
   <si>
     <t>./papers/65.pdf</t>
   </si>
   <si>
-    <t>Big Five Personality Traits; OCEAN; personality-adaptive conversational agents</t>
-  </si>
-  <si>
-    <t>Big Five personality profiles shape the system architecture and response adaptation.</t>
-  </si>
-  <si>
-    <t>Big Five Personality Traits; personality classification accuracy; personality-adapted response</t>
-  </si>
-  <si>
-    <t>Evaluation evidence includes Big Five classification accuracy and adapted response generation, but therapy-quality evaluation of personality adaptation is limited.</t>
-  </si>
-  <si>
-    <t>p.1 Abstract/Method summary</t>
-  </si>
-  <si>
-    <t>Theory-specific benchmark/task</t>
-  </si>
-  <si>
-    <t>No human perception, learning, clinical, or deployment outcome measure found.</t>
-  </si>
-  <si>
-    <t>Evaluation sections checked</t>
-  </si>
-  <si>
-    <t>A formal personality construct is evaluated at classifier/task level, but depth is limited for counseling evaluation.</t>
+    <t xml:space="preserve">Big Five Personality Traits; OCEAN; personality-adaptive conversational agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Five personality profiles shape the system architecture and response adaptation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Five Personality Traits; personality classification accuracy; personality-adapted response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation evidence includes Big Five classification accuracy and adapted response generation, but therapy-quality evaluation of personality adaptation is limited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.1 Abstract/Method summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-specific benchmark/task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No human perception, learning, clinical, or deployment outcome measure found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation sections checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A formal personality construct is evaluated at classifier/task level, but depth is limited for counseling evaluation.</t>
   </si>
   <si>
     <t>Xu2025MentalChat16K</t>
   </si>
   <si>
-    <t>MentalChat16K: A Benchmark Dataset for Conversational Mental Health Assistance</t>
+    <t xml:space="preserve">MentalChat16K: A Benchmark Dataset for Conversational Mental Health Assistance</t>
   </si>
   <si>
     <t>./papers/68.pdf</t>
   </si>
   <si>
-    <t>Miller and Moyers active listening; EPITOME empathy metrics; Rogers therapeutic principles; Dialogue Safety; PsyEval</t>
-  </si>
-  <si>
-    <t>MentalChat16K evaluation metrics synthesize validated counseling/support frameworks and therapeutic principles.</t>
-  </si>
-  <si>
-    <t>p.5 Metrics</t>
-  </si>
-  <si>
-    <t>Active Listening; EPITOME empathy; Rogers therapeutic principles; Safety &amp; Trustworthiness; PsyEval; Dialogue Safety</t>
-  </si>
-  <si>
-    <t>Evaluation dimensions include Active Listening, Empathy &amp; Validation, Safety &amp; Trustworthiness, open-mindedness, and non-judgment, derived from prior validated frameworks.</t>
-  </si>
-  <si>
-    <t>p.5 Evaluation metrics</t>
-  </si>
-  <si>
-    <t>Theory-specific rubric; LLM judge with theory-specific criteria; Theory-specific benchmark/task</t>
-  </si>
-  <si>
-    <t>No downstream human or clinical consequence is measured.</t>
-  </si>
-  <si>
-    <t>Construct-specific support/counseling metrics define evaluation.</t>
+    <t xml:space="preserve">Miller and Moyers active listening; EPITOME empathy metrics; Rogers therapeutic principles; Dialogue Safety; PsyEval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MentalChat16K evaluation metrics synthesize validated counseling/support frameworks and therapeutic principles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5 Metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Listening; EPITOME empathy; Rogers therapeutic principles; Safety &amp; Trustworthiness; PsyEval; Dialogue Safety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation dimensions include Active Listening, Empathy &amp; Validation, Safety &amp; Trustworthiness, open-mindedness, and non-judgment, derived from prior validated frameworks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5 Evaluation metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-specific rubric; LLM judge with theory-specific criteria; Theory-specific benchmark/task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream human or clinical consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Construct-specific support/counseling metrics define evaluation.</t>
   </si>
   <si>
     <t>Schmidmaier2025Using</t>
   </si>
   <si>
-    <t>Using a Secondary Channel to Display the Internal Empathic Resonance of LLM-Driven Agents for Mental Health Support</t>
+    <t xml:space="preserve">Using a Secondary Channel to Display the Internal Empathic Resonance of LLM-Driven Agents for Mental Health Support</t>
   </si>
   <si>
     <t>./papers/69.pdf</t>
   </si>
   <si>
-    <t>empathy; empathic resonance; therapeutic alliance; PETS; perceived empathy</t>
-  </si>
-  <si>
-    <t>The interface and research question are grounded in cognitive/affective empathy and therapeutic alliance literature.</t>
+    <t xml:space="preserve">empathy; empathic resonance; therapeutic alliance; PETS; perceived empathy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The interface and research question are grounded in cognitive/affective empathy and therapeutic alliance literature.</t>
   </si>
   <si>
     <t>pp.1-4</t>
   </si>
   <si>
-    <t>PETS; perceived empathy; empathic resonance; cognitive empathy; affective empathy</t>
-  </si>
-  <si>
-    <t>User study evaluates perceived empathy with PETS/PETS subscales and compares display of internal empathic resonance.</t>
-  </si>
-  <si>
-    <t>pp.6-8 Results/PETS analysis</t>
-  </si>
-  <si>
-    <t>Validated scale; HCI/perception construct scale</t>
-  </si>
-  <si>
-    <t>Human perception</t>
-  </si>
-  <si>
-    <t>The consequence measured is human perceived empathy and engagement with the system.</t>
+    <t xml:space="preserve">PETS; perceived empathy; empathic resonance; cognitive empathy; affective empathy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User study evaluates perceived empathy with PETS/PETS subscales and compares display of internal empathic resonance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.6-8 Results/PETS analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; HCI/perception construct scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human perception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The consequence measured is human perceived empathy and engagement with the system.</t>
   </si>
   <si>
     <t>pp.6-8</t>
   </si>
   <si>
-    <t>A perception construct scale operationalizes empathy evaluation.</t>
+    <t xml:space="preserve">A perception construct scale operationalizes empathy evaluation.</t>
   </si>
   <si>
     <t>Schmidmaier2025UsingNonverbal</t>
   </si>
   <si>
-    <t>Using Nonverbal Cues in Empathic Multi-Modal LLM-Driven Chatbots for Mental Health Support</t>
+    <t xml:space="preserve">Using Nonverbal Cues in Empathic Multi-Modal LLM-Driven Chatbots for Mental Health Support</t>
   </si>
   <si>
     <t>./papers/71.pdf</t>
   </si>
   <si>
-    <t>empathy; nonverbal communication; facial expression recognition; PETS; LIWC psychological processes</t>
-  </si>
-  <si>
-    <t>Empathy and nonverbal communication theory shape multimodal chatbot design and evaluation.</t>
+    <t xml:space="preserve">empathy; nonverbal communication; facial expression recognition; PETS; LIWC psychological processes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empathy and nonverbal communication theory shape multimodal chatbot design and evaluation.</t>
   </si>
   <si>
     <t>pp.2-6</t>
   </si>
   <si>
-    <t>PETS; perceived empathy; facial expression recognition; LIWC affect/emotion categories; nonverbal communication</t>
-  </si>
-  <si>
-    <t>Evaluation uses PETS perceived-empathy ratings, FER accuracy/F1, and LIWC affective/psychological-process measures.</t>
-  </si>
-  <si>
-    <t>pp.7-16; Appendix C</t>
-  </si>
-  <si>
-    <t>Validated scale; HCI/perception construct scale; Affective/emotional dynamics metric</t>
-  </si>
-  <si>
-    <t>The study measures user perceived empathy/nonverbal communication and interaction behavior.</t>
-  </si>
-  <si>
-    <t>pp.12-14 Results</t>
-  </si>
-  <si>
-    <t>Formal perceived-empathy and affective measures define evaluation.</t>
+    <t xml:space="preserve">PETS; perceived empathy; facial expression recognition; LIWC affect/emotion categories; nonverbal communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses PETS perceived-empathy ratings, FER accuracy/F1, and LIWC affective/psychological-process measures.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.7-16; Appendix C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; HCI/perception construct scale; Affective/emotional dynamics metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The study measures user perceived empathy/nonverbal communication and interaction behavior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.12-14 Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formal perceived-empathy and affective measures define evaluation.</t>
   </si>
   <si>
     <t>Ozgun2025Trustworthy</t>
   </si>
   <si>
-    <t>Trustworthy AI Psychotherapy: Multi-Agent LLM Workflow for Counseling and Explainable Mental Disorder DiagNosis</t>
+    <t xml:space="preserve">Trustworthy AI Psychotherapy: Multi-Agent LLM Workflow for Counseling and Explainable Mental Disorder DiagNosis</t>
   </si>
   <si>
     <t>./papers/72.pdf</t>
   </si>
   <si>
-    <t>DSM-5; mental-disorder diagnosis; empathy/professional tone; clinical classification</t>
-  </si>
-  <si>
-    <t>DSM-5 diagnostic dimensions shape the multi-agent diagnosis/counseling workflow and rubric.</t>
-  </si>
-  <si>
-    <t>p.4 Rubric/Metrics</t>
-  </si>
-  <si>
-    <t>DSM-5 dimension coverage; DSM-5 codes; diagnostic classification; empathy/professional tone</t>
-  </si>
-  <si>
-    <t>Evaluation uses DSM-5 dimension coverage in therapist-client rubric and precision/recall/F1/ROC-AUC for predicted DSM-5 codes.</t>
-  </si>
-  <si>
-    <t>p.4 Table 1 and metrics</t>
-  </si>
-  <si>
-    <t>Evaluation is diagnostic/model performance, not a downstream patient or deployment outcome.</t>
-  </si>
-  <si>
-    <t>DSM-5 criteria define both rubric and metrics.</t>
+    <t xml:space="preserve">DSM-5; mental-disorder diagnosis; empathy/professional tone; clinical classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSM-5 diagnostic dimensions shape the multi-agent diagnosis/counseling workflow and rubric.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.4 Rubric/Metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSM-5 dimension coverage; DSM-5 codes; diagnostic classification; empathy/professional tone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses DSM-5 dimension coverage in therapist-client rubric and precision/recall/F1/ROC-AUC for predicted DSM-5 codes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.4 Table 1 and metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation is diagnostic/model performance, not a downstream patient or deployment outcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSM-5 criteria define both rubric and metrics.</t>
   </si>
   <si>
     <t>Louie2026Can</t>
   </si>
   <si>
-    <t>Can LLM-Simulated Practice and Feedback Upskill Human Counselors? A Randomized Study with 90+ Novice Counselors</t>
+    <t xml:space="preserve">Can LLM-Simulated Practice and Feedback Upskill Human Counselors? A Randomized Study with 90+ Novice Counselors</t>
   </si>
   <si>
     <t>./papers/75.pdf</t>
   </si>
   <si>
-    <t>client-centered approaches; therapeutic alliance; active listening; reflections; counselor competence; counselor skill acquisition</t>
-  </si>
-  <si>
-    <t>The intervention targets counselor skills linked to client-centered approaches and therapeutic alliance/common factors.</t>
-  </si>
-  <si>
-    <t>pp.1, 17</t>
-  </si>
-  <si>
-    <t>counselor competence; active listening; reflections; questions; counselor skill acquisition; performance standards</t>
-  </si>
-  <si>
-    <t>Randomized evaluation measures novice counselor performance/skill use after LLM-simulated practice and feedback.</t>
-  </si>
-  <si>
-    <t>pp.1, 17 Results/Discussion</t>
-  </si>
-  <si>
-    <t>Human behavior/outcome measure; Theory-specific rubric; Custom expert rating</t>
-  </si>
-  <si>
-    <t>Human learning/skill</t>
-  </si>
-  <si>
-    <t>The study measures whether novice counselors improve in counseling performance/skill use after training.</t>
-  </si>
-  <si>
-    <t>Results/Discussion sections</t>
-  </si>
-  <si>
-    <t>Theory-related counseling skills are evaluated as human learning/skill outcomes.</t>
+    <t xml:space="preserve">client-centered approaches; therapeutic alliance; active listening; reflections; counselor competence; counselor skill acquisition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The intervention targets counselor skills linked to client-centered approaches and therapeutic alliance/common factors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">counselor competence; active listening; reflections; questions; counselor skill acquisition; performance standards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Randomized evaluation measures novice counselor performance/skill use after LLM-simulated practice and feedback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 17 Results/Discussion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human behavior/outcome measure; Theory-specific rubric; Custom expert rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human learning/skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The study measures whether novice counselors improve in counseling performance/skill use after training.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Results/Discussion sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-related counseling skills are evaluated as human learning/skill outcomes.</t>
   </si>
   <si>
     <t>Kuhail2025Human-Human</t>
   </si>
   <si>
-    <t>Human-Human vs Human-AI Therapy: An Empirical Study</t>
+    <t xml:space="preserve">Human-Human vs Human-AI Therapy: An Empirical Study</t>
   </si>
   <si>
     <t>./papers/77.pdf</t>
@@ -1088,628 +1083,628 @@
     <t>Mentioned</t>
   </si>
   <si>
-    <t>CBT; empathy; therapeutic interaction</t>
-  </si>
-  <si>
-    <t>CBT and empathy appear in background discussion of therapy chatbots, but do not visibly shape the method/evaluation.</t>
+    <t xml:space="preserve">CBT; empathy; therapeutic interaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT and empathy appear in background discussion of therapy chatbots, but do not visibly shape the method/evaluation.</t>
   </si>
   <si>
     <t>pp.3-6</t>
   </si>
   <si>
-    <t>Evaluation is human-vs-AI transcript perception and qualitative themes, not a theory-specific metric or rubric.</t>
-  </si>
-  <si>
-    <t>pp.4-6 Results</t>
-  </si>
-  <si>
-    <t>Theory is background-only for the evaluation question.</t>
+    <t xml:space="preserve">Evaluation is human-vs-AI transcript perception and qualitative themes, not a theory-specific metric or rubric.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.4-6 Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory is background-only for the evaluation question.</t>
   </si>
   <si>
     <t>Louie2024Roleplay-doh</t>
   </si>
   <si>
-    <t>Roleplay-doh: Enabling Domain-Experts to Create LLM-simulated Patients via Eliciting and Adhering to Principles</t>
+    <t xml:space="preserve">Roleplay-doh: Enabling Domain-Experts to Create LLM-simulated Patients via Eliciting and Adhering to Principles</t>
   </si>
   <si>
     <t>./papers/80.pdf</t>
   </si>
   <si>
-    <t>expert-defined role-play principles; patient simulation; principle adherence</t>
-  </si>
-  <si>
-    <t>Domain experts create patient simulation principles, but these are not clearly tied to a formal theory/framework.</t>
-  </si>
-  <si>
-    <t>p.8 Evaluation of Principle-Adherence</t>
-  </si>
-  <si>
-    <t>principle adherence; patient description consistency; awkward speech; expert counselor rankings</t>
-  </si>
-  <si>
-    <t>Expert counselors rate consistency and adherence to expert-defined patient principles using custom M1/M2/M3 metrics.</t>
-  </si>
-  <si>
-    <t>No downstream trainee learning or clinical outcome is measured.</t>
-  </si>
-  <si>
-    <t>Principle-adherence is theory-relevant but custom and weaker than established scale/coding evaluation.</t>
+    <t xml:space="preserve">expert-defined role-play principles; patient simulation; principle adherence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain experts create patient simulation principles, but these are not clearly tied to a formal theory/framework.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.8 Evaluation of Principle-Adherence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">principle adherence; patient description consistency; awkward speech; expert counselor rankings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expert counselors rate consistency and adherence to expert-defined patient principles using custom M1/M2/M3 metrics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream trainee learning or clinical outcome is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principle-adherence is theory-relevant but custom and weaker than established scale/coding evaluation.</t>
   </si>
   <si>
     <t>Wang2024PATIENT</t>
   </si>
   <si>
-    <t>PATIENT-?: Using Large Language Models to Simulate Patients for Training Mental Health Professionals</t>
+    <t xml:space="preserve">PATIENT-?: Using Large Language Models to Simulate Patients for Training Mental Health Professionals</t>
   </si>
   <si>
     <t>./papers/81.pdf</t>
   </si>
   <si>
-    <t>CBT; CBT cognitive models; CBT formulation skills; therapeutic alliance</t>
-  </si>
-  <si>
-    <t>CBT cognitive models program simulated patients and support CBT formulation training.</t>
-  </si>
-  <si>
-    <t>pp.2, 9, 18</t>
-  </si>
-  <si>
-    <t>CBT cognitive models; CBT formulation skills; patient realism; trainee/professional evaluation</t>
-  </si>
-  <si>
-    <t>Evaluation is conducted with mental-health trainees/professionals in the context of CBT formulation and simulated patient realism.</t>
-  </si>
-  <si>
-    <t>p.9 Evaluation statement; method/evaluation sections</t>
-  </si>
-  <si>
-    <t>No direct measurement of trainee skill gain was found.</t>
-  </si>
-  <si>
-    <t>CBT formulation defines the benchmark/training evaluation, but no learning outcome is measured.</t>
+    <t xml:space="preserve">CBT; CBT cognitive models; CBT formulation skills; therapeutic alliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT cognitive models program simulated patients and support CBT formulation training.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 9, 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT cognitive models; CBT formulation skills; patient realism; trainee/professional evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation is conducted with mental-health trainees/professionals in the context of CBT formulation and simulated patient realism.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.9 Evaluation statement; method/evaluation sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No direct measurement of trainee skill gain was found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT formulation defines the benchmark/training evaluation, but no learning outcome is measured.</t>
   </si>
   <si>
     <t>Lee2024CACTUS</t>
   </si>
   <si>
-    <t>CACTUS: Towards Psychological Counseling Conversations using Cognitive Behavioral Theory</t>
+    <t xml:space="preserve">CACTUS: Towards Psychological Counseling Conversations using Cognitive Behavioral Theory</t>
   </si>
   <si>
     <t>./papers/83.pdf</t>
   </si>
   <si>
-    <t>CBT; CTRS; Cognitive Therapy Rating Scale; CBT techniques; counseling skill; empathy/helpfulness</t>
-  </si>
-  <si>
-    <t>CACTUS uses CBT planning/techniques to generate counseling conversations.</t>
-  </si>
-  <si>
-    <t>pp.5-6, 14</t>
-  </si>
-  <si>
-    <t>CTRS; CBT-specific skills; general counseling skills; empathy; helpfulness; CounselingEval</t>
-  </si>
-  <si>
-    <t>Evaluation uses CTRS/CounselingEval-style criteria for general counseling and CBT-specific skills, with G-Eval/Likert scoring.</t>
-  </si>
-  <si>
-    <t>pp.5-6; Appendix D</t>
-  </si>
-  <si>
-    <t>Established therapy/counseling coding system; Theory-specific rubric; LLM judge with theory-specific criteria; Theory-specific benchmark/task</t>
-  </si>
-  <si>
-    <t>The paper considers psychological changes in simulated clients rather than measured real-client outcomes.</t>
-  </si>
-  <si>
-    <t>p.5 Experiments/Evaluation design</t>
-  </si>
-  <si>
-    <t>CBT-specific skills are evaluated with established/customized counseling criteria.</t>
+    <t xml:space="preserve">CBT; CTRS; Cognitive Therapy Rating Scale; CBT techniques; counseling skill; empathy/helpfulness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACTUS uses CBT planning/techniques to generate counseling conversations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.5-6, 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTRS; CBT-specific skills; general counseling skills; empathy; helpfulness; CounselingEval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses CTRS/CounselingEval-style criteria for general counseling and CBT-specific skills, with G-Eval/Likert scoring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.5-6; Appendix D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Established therapy/counseling coding system; Theory-specific rubric; LLM judge with theory-specific criteria; Theory-specific benchmark/task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper considers psychological changes in simulated clients rather than measured real-client outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5 Experiments/Evaluation design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT-specific skills are evaluated with established/customized counseling criteria.</t>
   </si>
   <si>
     <t>Basar2024To</t>
   </si>
   <si>
-    <t>To What Extent Are Large Language Models Capable of Generating Substantial Reflections for Motivational Interviewing Counseling Chatbots?A Human Evaluation</t>
+    <t xml:space="preserve">To What Extent Are Large Language Models Capable of Generating Substantial Reflections for Motivational Interviewing Counseling Chatbots?A Human Evaluation</t>
   </si>
   <si>
     <t>./papers/84.pdf</t>
   </si>
   <si>
-    <t>motivational interviewing; MI reflections; empathy; therapeutic alliance</t>
-  </si>
-  <si>
-    <t>The task is generation and evaluation of substantial reflections for MI counseling chatbots.</t>
-  </si>
-  <si>
-    <t>p.1; p.4 Evaluation</t>
-  </si>
-  <si>
-    <t>MI reflections; appropriateness; specificity; empathy; naturalness; engagement</t>
-  </si>
-  <si>
-    <t>Human evaluation rates reflection quality dimensions such as appropriateness, specificity, empathy, naturalness, and engagement, but not with a formal MI fidelity coding system.</t>
-  </si>
-  <si>
-    <t>p.4 Human Evaluation</t>
-  </si>
-  <si>
-    <t>No client behavior change, counselor learning, or therapy outcome is measured.</t>
-  </si>
-  <si>
-    <t>MI grounds the task, but evaluation depth is custom reflection-quality ratings.</t>
+    <t xml:space="preserve">motivational interviewing; MI reflections; empathy; therapeutic alliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The task is generation and evaluation of substantial reflections for MI counseling chatbots.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.1; p.4 Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI reflections; appropriateness; specificity; empathy; naturalness; engagement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human evaluation rates reflection quality dimensions such as appropriateness, specificity, empathy, naturalness, and engagement, but not with a formal MI fidelity coding system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.4 Human Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No client behavior change, counselor learning, or therapy outcome is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI grounds the task, but evaluation depth is custom reflection-quality ratings.</t>
   </si>
   <si>
     <t>Yang2025Consistent</t>
   </si>
   <si>
-    <t>Consistent Client Simulation for Motivational Interviewing-based Counseling</t>
+    <t xml:space="preserve">Consistent Client Simulation for Motivational Interviewing-based Counseling</t>
   </si>
   <si>
     <t>./papers/86.pdf</t>
   </si>
   <si>
-    <t>motivational interviewing; MI client receptivity; receptivity levels; counseling outcomes</t>
-  </si>
-  <si>
-    <t>The client simulation framework is designed for MI-based counseling and receptivity dynamics.</t>
+    <t xml:space="preserve">motivational interviewing; MI client receptivity; receptivity levels; counseling outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The client simulation framework is designed for MI-based counseling and receptivity dynamics.</t>
   </si>
   <si>
     <t>pp.8-9</t>
   </si>
   <si>
-    <t>MI receptivity; receptivity score; ground-truth receptivity; Spearman correlation</t>
-  </si>
-  <si>
-    <t>Evaluation uses annotated client receptivity scores and correlation to ground truth, but receptivity scoring is custom rather than a validated MI coding instrument.</t>
-  </si>
-  <si>
-    <t>p.8 Evaluation; p.9 Ethics/Framework discussion</t>
-  </si>
-  <si>
-    <t>No downstream client or trainee outcome is measured.</t>
-  </si>
-  <si>
-    <t>Receptivity is theory-relevant, but the metric is custom and weaker than MITI/MISC-style coding.</t>
+    <t xml:space="preserve">MI receptivity; receptivity score; ground-truth receptivity; Spearman correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses annotated client receptivity scores and correlation to ground truth, but receptivity scoring is custom rather than a validated MI coding instrument.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.8 Evaluation; p.9 Ethics/Framework discussion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream client or trainee outcome is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receptivity is theory-relevant, but the metric is custom and weaker than MITI/MISC-style coding.</t>
   </si>
   <si>
     <t>Yang2025CAMI</t>
   </si>
   <si>
-    <t>CAMI: A Counselor Agent Supporting Motivational Interviewing through State Inference and Topic Exploration</t>
+    <t xml:space="preserve">CAMI: A Counselor Agent Supporting Motivational Interviewing through State Inference and Topic Exploration</t>
   </si>
   <si>
     <t>./papers/87.pdf</t>
   </si>
   <si>
-    <t>motivational interviewing; MI competence; WAI-SR; CECS; therapeutic alliance; session outcome</t>
-  </si>
-  <si>
-    <t>CAMI supports MI via state inference/topic exploration and evaluates MI competence and client experience.</t>
-  </si>
-  <si>
-    <t>p.18 Appendix C</t>
-  </si>
-  <si>
-    <t>MI competence; CECS; WAI-SR; therapeutic alliance; session outcome; self-reported feelings</t>
-  </si>
-  <si>
-    <t>Client experience evaluation uses CECS/WAI-SR-inspired questionnaires for session outcomes, therapeutic alliance, and self-reported feelings, alongside MI competence.</t>
-  </si>
-  <si>
-    <t>p.18 Appendix C Client Experience Evaluation</t>
-  </si>
-  <si>
-    <t>Validated scale; Theory-specific rubric; HCI/perception construct scale</t>
-  </si>
-  <si>
-    <t>Session outcome/alliance/feelings are assessed for generated/simulated sessions rather than real-client therapy outcomes.</t>
-  </si>
-  <si>
-    <t>Validated alliance/client-experience instruments shape evaluation, but consequences are simulated.</t>
+    <t xml:space="preserve">motivational interviewing; MI competence; WAI-SR; CECS; therapeutic alliance; session outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMI supports MI via state inference/topic exploration and evaluates MI competence and client experience.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.18 Appendix C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI competence; CECS; WAI-SR; therapeutic alliance; session outcome; self-reported feelings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client experience evaluation uses CECS/WAI-SR-inspired questionnaires for session outcomes, therapeutic alliance, and self-reported feelings, alongside MI competence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.18 Appendix C Client Experience Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; Theory-specific rubric; HCI/perception construct scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session outcome/alliance/feelings are assessed for generated/simulated sessions rather than real-client therapy outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated alliance/client-experience instruments shape evaluation, but consequences are simulated.</t>
   </si>
   <si>
     <t>Xie2025PsyDT</t>
   </si>
   <si>
-    <t>PsyDT: Using LLMs to Construct the Digital Twin of Psychological Counselor with Personalized Counseling Style for Psychological Counseling</t>
+    <t xml:space="preserve">PsyDT: Using LLMs to Construct the Digital Twin of Psychological Counselor with Personalized Counseling Style for Psychological Counseling</t>
   </si>
   <si>
     <t>./papers/89.pdf</t>
   </si>
   <si>
-    <t>Big Five personality theory; OCEAN; client personality; counseling style; therapy technique</t>
-  </si>
-  <si>
-    <t>Big Five/OCEAN client personality and counselor style/therapy technique guide dialogue synthesis.</t>
-  </si>
-  <si>
-    <t>pp.1, 4</t>
-  </si>
-  <si>
-    <t>Checked evaluation evidence does not clearly use Big Five/personality traits as evaluation metrics; evaluation appears to focus on dialogue quality/style.</t>
-  </si>
-  <si>
-    <t>Formal personality theory shapes design, not evaluation.</t>
+    <t xml:space="preserve">Big Five personality theory; OCEAN; client personality; counseling style; therapy technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Five/OCEAN client personality and counselor style/therapy technique guide dialogue synthesis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked evaluation evidence does not clearly use Big Five/personality traits as evaluation metrics; evaluation appears to focus on dialogue quality/style.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formal personality theory shapes design, not evaluation.</t>
   </si>
   <si>
     <t>Kermani2025Systematic</t>
   </si>
   <si>
-    <t>A Systematic Evaluation of LLM Strategies for Mental Health Text Analysis: Fine-tuning vs. Prompt Engineering vs. RAG</t>
+    <t xml:space="preserve">A Systematic Evaluation of LLM Strategies for Mental Health Text Analysis: Fine-tuning vs. Prompt Engineering vs. RAG</t>
   </si>
   <si>
     <t>./papers/91.pdf</t>
   </si>
   <si>
-    <t>mental-health text analysis; emotion labels; clinical utility; assessment</t>
-  </si>
-  <si>
-    <t>Mental-health and emotion constructs structure the datasets and motivation, but no named clinical theory is central.</t>
-  </si>
-  <si>
-    <t>p.3 Evaluation frameworks/Datasets</t>
-  </si>
-  <si>
-    <t>mental-health labels; emotion labels; clinical utility; accuracy; F1</t>
-  </si>
-  <si>
-    <t>Evaluation uses mental-health/emotion classification datasets and conventional accuracy/F1 metrics; theory-specific construct definitions are limited.</t>
-  </si>
-  <si>
-    <t>p.3 Evaluation frameworks; Results</t>
-  </si>
-  <si>
-    <t>Theory-specific benchmark/task; Generic quality metric only</t>
-  </si>
-  <si>
-    <t>The labels are domain/theory-relevant, but evaluation depth is mostly standard classification.</t>
+    <t xml:space="preserve">mental-health text analysis; emotion labels; clinical utility; assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mental-health and emotion constructs structure the datasets and motivation, but no named clinical theory is central.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.3 Evaluation frameworks/Datasets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mental-health labels; emotion labels; clinical utility; accuracy; F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses mental-health/emotion classification datasets and conventional accuracy/F1 metrics; theory-specific construct definitions are limited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.3 Evaluation frameworks; Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory-specific benchmark/task; Generic quality metric only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The labels are domain/theory-relevant, but evaluation depth is mostly standard classification.</t>
   </si>
   <si>
     <t>Basar2025How</t>
   </si>
   <si>
-    <t>How Well Can Large Language Models Reflect? A Human Evaluation of LLM-generated Reflections for Motivational Interviewing Dialogues</t>
+    <t xml:space="preserve">How Well Can Large Language Models Reflect? A Human Evaluation of LLM-generated Reflections for Motivational Interviewing Dialogues</t>
   </si>
   <si>
     <t>./papers/92.pdf</t>
   </si>
   <si>
-    <t>motivational interviewing; MI reflections; therapeutic alliance; empathy</t>
-  </si>
-  <si>
-    <t>The paper studies MI reflection generation and uses MI instructions in prompts.</t>
-  </si>
-  <si>
-    <t>pp.1, 9</t>
-  </si>
-  <si>
-    <t>MI reflections; empathy; therapeutic alliance; reflection quality criteria</t>
-  </si>
-  <si>
-    <t>Evaluation rates MI reflection quality, but the paper notes future work should include MI experts and additional empathy/therapeutic-alliance metrics.</t>
-  </si>
-  <si>
-    <t>p.9 Discussion/Future work; evaluation sections</t>
-  </si>
-  <si>
-    <t>No client behavior, counselor learning, or therapeutic outcome is measured.</t>
-  </si>
-  <si>
-    <t>MI is central, but evaluation is custom and not a full MI fidelity scale.</t>
+    <t xml:space="preserve">motivational interviewing; MI reflections; therapeutic alliance; empathy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper studies MI reflection generation and uses MI instructions in prompts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI reflections; empathy; therapeutic alliance; reflection quality criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation rates MI reflection quality, but the paper notes future work should include MI experts and additional empathy/therapeutic-alliance metrics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.9 Discussion/Future work; evaluation sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No client behavior, counselor learning, or therapeutic outcome is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI is central, but evaluation is custom and not a full MI fidelity scale.</t>
   </si>
   <si>
     <t>Feng2025Reframe</t>
   </si>
   <si>
-    <t>Reframe Your Life Story: Interactive Narrative Therapist and InNovative Moment Assessment with Large Language Models</t>
+    <t xml:space="preserve">Reframe Your Life Story: Interactive Narrative Therapist and InNovative Moment Assessment with Large Language Models</t>
   </si>
   <si>
     <t>./papers/93.pdf</t>
   </si>
   <si>
-    <t>narrative therapy; Innovative Moments Assessment; IMA/IMCS; therapeutic progression; dynamic state planning</t>
-  </si>
-  <si>
-    <t>Narrative therapy and dynamic state planning shape the system, with IMA used for progression-aware evaluation.</t>
-  </si>
-  <si>
-    <t>pp.2, 4</t>
-  </si>
-  <si>
-    <t>Innovative Moments Assessment; IMA/IMCS; narrative therapy; therapeutic progression; innovative moments</t>
-  </si>
-  <si>
-    <t>Evaluation uses Innovative Moments as a theoretical construct to assess therapeutic progression in dialogue.</t>
-  </si>
-  <si>
-    <t>p.4 Section 3.3 IMA for Evaluation</t>
-  </si>
-  <si>
-    <t>Therapeutic progression is assessed in simulated/generated dialogue rather than real client outcome.</t>
-  </si>
-  <si>
-    <t>p.4 Evaluation; Results</t>
-  </si>
-  <si>
-    <t>Narrative-therapy innovative moments define evaluation.</t>
+    <t xml:space="preserve">narrative therapy; Innovative Moments Assessment; IMA/IMCS; therapeutic progression; dynamic state planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative therapy and dynamic state planning shape the system, with IMA used for progression-aware evaluation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovative Moments Assessment; IMA/IMCS; narrative therapy; therapeutic progression; innovative moments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses Innovative Moments as a theoretical construct to assess therapeutic progression in dialogue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.4 Section 3.3 IMA for Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapeutic progression is assessed in simulated/generated dialogue rather than real client outcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.4 Evaluation; Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative-therapy innovative moments define evaluation.</t>
   </si>
   <si>
     <t>Xu2025MultiAgentESC</t>
   </si>
   <si>
-    <t>MultiAgentESC: A LLM-based Multi-Agent Collaboration Framework for Emotional Support Conversation</t>
+    <t xml:space="preserve">MultiAgentESC: A LLM-based Multi-Agent Collaboration Framework for Emotional Support Conversation</t>
   </si>
   <si>
     <t>./papers/94.pdf</t>
   </si>
   <si>
-    <t>social interdependence theory; Helping Skills Theory; emotional support strategies; psychological state</t>
-  </si>
-  <si>
-    <t>Social interdependence and Helping Skills Theory motivate multi-agent emotional-support design.</t>
+    <t xml:space="preserve">social interdependence theory; Helping Skills Theory; emotional support strategies; psychological state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social interdependence and Helping Skills Theory motivate multi-agent emotional-support design.</t>
   </si>
   <si>
     <t>pp.2-4</t>
   </si>
   <si>
-    <t>Checked evaluation relies mainly on automatic response-generation metrics and does not clearly evaluate Helping Skills or social-interdependence constructs.</t>
-  </si>
-  <si>
-    <t>pp.5-6 Evaluation/Results</t>
-  </si>
-  <si>
-    <t>Named theories shape design, but not evaluation.</t>
+    <t xml:space="preserve">Checked evaluation relies mainly on automatic response-generation metrics and does not clearly evaluate Helping Skills or social-interdependence constructs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.5-6 Evaluation/Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named theories shape design, but not evaluation.</t>
   </si>
   <si>
     <t>Kim2025MIRROR</t>
   </si>
   <si>
-    <t>MIRROR: Multimodal Cognitive Reframing Therapy for Rolling with Resistance</t>
+    <t xml:space="preserve">MIRROR: Multimodal Cognitive Reframing Therapy for Rolling with Resistance</t>
   </si>
   <si>
     <t>./papers/95.pdf</t>
   </si>
   <si>
-    <t>CBT; cognitive reframing; client resistance; therapeutic alliance; COUNSELING EVAL</t>
-  </si>
-  <si>
-    <t>MIRROR applies multimodal cognitive reframing therapy to rolling with resistance in CBT.</t>
-  </si>
-  <si>
-    <t>pp.1-2, 6</t>
-  </si>
-  <si>
-    <t>CBT; COUNSELING EVAL; client resistance; therapeutic alliance; therapist skills; CBT-specific competencies</t>
-  </si>
-  <si>
-    <t>Evaluation assesses resistance management through therapist skills and client alliance, using COUNSELING EVAL for general counseling and CBT-specific competencies.</t>
-  </si>
-  <si>
-    <t>p.6 Metrics for Assessment</t>
-  </si>
-  <si>
-    <t>Established therapy/counseling coding system; Theory-specific rubric; Custom expert rating</t>
-  </si>
-  <si>
-    <t>Alliance/resistance outcomes are measured in simulated interactions, not real therapy outcomes.</t>
-  </si>
-  <si>
-    <t>p.6 Evaluation/Results</t>
-  </si>
-  <si>
-    <t>CBT resistance and alliance are explicit evaluation constructs.</t>
+    <t xml:space="preserve">CBT; cognitive reframing; client resistance; therapeutic alliance; COUNSELING EVAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRROR applies multimodal cognitive reframing therapy to rolling with resistance in CBT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1-2, 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT; COUNSELING EVAL; client resistance; therapeutic alliance; therapist skills; CBT-specific competencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation assesses resistance management through therapist skills and client alliance, using COUNSELING EVAL for general counseling and CBT-specific competencies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.6 Metrics for Assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Established therapy/counseling coding system; Theory-specific rubric; Custom expert rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alliance/resistance outcomes are measured in simulated interactions, not real therapy outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.6 Evaluation/Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT resistance and alliance are explicit evaluation constructs.</t>
   </si>
   <si>
     <t>Kim2025Can</t>
   </si>
   <si>
-    <t>Can You Share Your Story? Modeling Clients' Metacognition and Openness for LLM Therapist Evaluation</t>
+    <t xml:space="preserve">Can You Share Your Story? Modeling Clients' Metacognition and Openness for LLM Therapist Evaluation</t>
   </si>
   <si>
     <t>./papers/97.pdf</t>
   </si>
   <si>
-    <t>CBT; CTRS; openness; metacognition; self-disclosure; exploration ability</t>
-  </si>
-  <si>
-    <t>The client simulator models openness and metacognition to evaluate therapist exploration in CBT-based counseling.</t>
-  </si>
-  <si>
-    <t>pp.2, 13</t>
-  </si>
-  <si>
-    <t>CTRS; CBT-based counseling; openness; metacognition; exploration ability</t>
-  </si>
-  <si>
-    <t>Evaluation uses CTRS items for CBT-based counseling quality and tracks openness/metacognition dynamics in the simulator.</t>
-  </si>
-  <si>
-    <t>p.13 Appendix C.2 CTRS</t>
-  </si>
-  <si>
-    <t>Established therapy/counseling coding system; Theory-specific rubric; Theory-specific benchmark/task</t>
-  </si>
-  <si>
-    <t>Outcome-like changes are simulated client openness/metacognition/session dynamics, not real client outcomes.</t>
-  </si>
-  <si>
-    <t>Formal CBT counseling scale and modeled client constructs define evaluation.</t>
+    <t xml:space="preserve">CBT; CTRS; openness; metacognition; self-disclosure; exploration ability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The client simulator models openness and metacognition to evaluate therapist exploration in CBT-based counseling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTRS; CBT-based counseling; openness; metacognition; exploration ability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses CTRS items for CBT-based counseling quality and tracks openness/metacognition dynamics in the simulator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.13 Appendix C.2 CTRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Established therapy/counseling coding system; Theory-specific rubric; Theory-specific benchmark/task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome-like changes are simulated client openness/metacognition/session dynamics, not real client outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formal CBT counseling scale and modeled client constructs define evaluation.</t>
   </si>
   <si>
     <t>Liu2025Eeyore</t>
   </si>
   <si>
-    <t>Eeyore: Realistic Depression Simulation via Expert-in-the-Loop Supervised and Preference Optimization</t>
+    <t xml:space="preserve">Eeyore: Realistic Depression Simulation via Expert-in-the-Loop Supervised and Preference Optimization</t>
   </si>
   <si>
     <t>./papers/99.pdf</t>
   </si>
   <si>
-    <t>DSM-V; Beck cognitive theory; cognitive distortions; PHQ-9; depression severity; DBI</t>
-  </si>
-  <si>
-    <t>Depression simulation profiles are structured from DSM-V symptoms, Beck cognitive distortions, and PHQ-9/DBI-inspired severity.</t>
-  </si>
-  <si>
-    <t>p.5 Profile construction</t>
-  </si>
-  <si>
-    <t>DSM-V depression symptoms; Beck cognitive distortions; PHQ-9; DBI; depression severity labels</t>
-  </si>
-  <si>
-    <t>Evaluation and profile extraction use structured depression symptoms, cognitive distortion labels, and severity categories inspired by clinical instruments.</t>
-  </si>
-  <si>
-    <t>p.5; p.7 Evaluation setup</t>
-  </si>
-  <si>
-    <t>Clinical diagnostic benchmark; Theory-specific benchmark/task; Custom expert rating</t>
-  </si>
-  <si>
-    <t>Outcomes are simulated depression profile/severity realism rather than real patient symptom change.</t>
-  </si>
-  <si>
-    <t>p.7 Evaluation</t>
-  </si>
-  <si>
-    <t>Clinical symptom/distortion labels define the simulation and evaluation targets.</t>
+    <t xml:space="preserve">DSM-V; Beck cognitive theory; cognitive distortions; PHQ-9; depression severity; DBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression simulation profiles are structured from DSM-V symptoms, Beck cognitive distortions, and PHQ-9/DBI-inspired severity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5 Profile construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSM-V depression symptoms; Beck cognitive distortions; PHQ-9; DBI; depression severity labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation and profile extraction use structured depression symptoms, cognitive distortion labels, and severity categories inspired by clinical instruments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5; p.7 Evaluation setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical diagnostic benchmark; Theory-specific benchmark/task; Custom expert rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcomes are simulated depression profile/severity realism rather than real patient symptom change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.7 Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical symptom/distortion labels define the simulation and evaluation targets.</t>
   </si>
   <si>
     <t>Wang2025Feel</t>
   </si>
   <si>
-    <t>Feel the Difference? A Comparative Analysis of Emotional Arcs in Real and LLM-Generated CBT Sessions</t>
+    <t xml:space="preserve">Feel the Difference? A Comparative Analysis of Emotional Arcs in Real and LLM-Generated CBT Sessions</t>
   </si>
   <si>
     <t>./papers/100.pdf</t>
   </si>
   <si>
-    <t>CBT; Utterance Emotion Dynamics; valence/arousal/dominance; emotion dynamics; emotional arcs</t>
-  </si>
-  <si>
-    <t>The paper analyzes authentic and generated CBT sessions using an emotion-dynamics framework.</t>
-  </si>
-  <si>
-    <t>Utterance Emotion Dynamics; valence/arousal/dominance; emotional arcs; CBT sessions</t>
-  </si>
-  <si>
-    <t>Evaluation/analysis compares fine-grained affective trajectories across valence, arousal, and dominance in real and generated CBT sessions.</t>
-  </si>
-  <si>
-    <t>p.1 Abstract/Introduction; p.4 Annotation</t>
-  </si>
-  <si>
-    <t>Affective/emotional dynamics metric; Theory-specific benchmark/task</t>
-  </si>
-  <si>
-    <t>The paper analyzes dialogue dynamics but does not assess downstream human or clinical consequences.</t>
-  </si>
-  <si>
-    <t>Evaluation/Analysis sections</t>
-  </si>
-  <si>
-    <t>Emotion-dynamics constructs explicitly define evaluation/analysis.</t>
+    <t xml:space="preserve">CBT; Utterance Emotion Dynamics; valence/arousal/dominance; emotion dynamics; emotional arcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper analyzes authentic and generated CBT sessions using an emotion-dynamics framework.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utterance Emotion Dynamics; valence/arousal/dominance; emotional arcs; CBT sessions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation/analysis compares fine-grained affective trajectories across valence, arousal, and dominance in real and generated CBT sessions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.1 Abstract/Introduction; p.4 Annotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affective/emotional dynamics metric; Theory-specific benchmark/task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper analyzes dialogue dynamics but does not assess downstream human or clinical consequences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation/Analysis sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emotion-dynamics constructs explicitly define evaluation/analysis.</t>
   </si>
   <si>
     <t>Samuel2025PersonaGym</t>
   </si>
   <si>
-    <t>PersonaGym: Evaluating Persona Agents and LLMs</t>
+    <t xml:space="preserve">PersonaGym: Evaluating Persona Agents and LLMs</t>
   </si>
   <si>
     <t>./papers/101.pdf</t>
   </si>
   <si>
-    <t>decision theory; persona consistency; PersonaScore; persona agents</t>
-  </si>
-  <si>
-    <t>PersonaGym/PersonaScore are grounded in decision theory for evaluating persona-agent consistency.</t>
+    <t xml:space="preserve">decision theory; persona consistency; PersonaScore; persona agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PersonaGym/PersonaScore are grounded in decision theory for evaluating persona-agent consistency.</t>
   </si>
   <si>
     <t>pp.1-2</t>
   </si>
   <si>
-    <t>decision theory; PersonaScore; persona consistency; human-aligned automatic metric</t>
-  </si>
-  <si>
-    <t>PersonaScore is a human-aligned automatic metric grounded in decision theory to evaluate whether persona agents act consistently with assigned personas.</t>
-  </si>
-  <si>
-    <t>pp.1-2 Method/Evaluation overview</t>
-  </si>
-  <si>
-    <t>Evaluation is persona-agent benchmark performance without downstream human consequence.</t>
-  </si>
-  <si>
-    <t>A formal decision-theoretic metric defines persona evaluation.</t>
+    <t xml:space="preserve">decision theory; PersonaScore; persona consistency; human-aligned automatic metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PersonaScore is a human-aligned automatic metric grounded in decision theory to evaluate whether persona agents act consistently with assigned personas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1-2 Method/Evaluation overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation is persona-agent benchmark performance without downstream human consequence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A formal decision-theoretic metric defines persona evaluation.</t>
   </si>
   <si>
     <t>Chen2025MIND</t>
   </si>
   <si>
-    <t>MIND: Towards Immersive Psychological Healing with Multi-Agent Inner Dialogue</t>
+    <t xml:space="preserve">MIND: Towards Immersive Psychological Healing with Multi-Agent Inner Dialogue</t>
   </si>
   <si>
     <t>./papers/102.pdf</t>
   </si>
   <si>
-    <t>self-empathy training; self-compassion; cognitive distortion; cognitive restructuring; PANAS</t>
-  </si>
-  <si>
-    <t>A multi-agent inner-dialogue system uses self-empathy/self-compassion and cognitive-distortion/restructuring constructs.</t>
-  </si>
-  <si>
-    <t>pp.2-7, 23-25</t>
-  </si>
-  <si>
-    <t>PANAS; cognitive distortion; cognitive restructuring; emotional relief; immersion; self-compassion</t>
-  </si>
-  <si>
-    <t>Evaluation measures mood/affect with PANAS and user-facing emotional relief/experience dimensions while prompts label cognitive distortions and restructuring methods.</t>
-  </si>
-  <si>
-    <t>pp.17-20 Evaluation metrics; pp.23-25 prompts</t>
-  </si>
-  <si>
-    <t>Validated scale; Human behavior/outcome measure; HCI/perception construct scale; Theory-specific rubric</t>
-  </si>
-  <si>
-    <t>The study measures real participant mood/affect change and emotional relief, although not in a clinical patient sample.</t>
-  </si>
-  <si>
-    <t>pp.17-20 User study/Evaluation metrics</t>
-  </si>
-  <si>
-    <t>Validated affect scale and participant mood change make this the closest real therapeutic-outcome measure; human check recommended for consequence label.</t>
+    <t xml:space="preserve">self-empathy training; self-compassion; cognitive distortion; cognitive restructuring; PANAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A multi-agent inner-dialogue system uses self-empathy/self-compassion and cognitive-distortion/restructuring constructs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2-7, 23-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANAS; cognitive distortion; cognitive restructuring; emotional relief; immersion; self-compassion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation measures mood/affect with PANAS and user-facing emotional relief/experience dimensions while prompts label cognitive distortions and restructuring methods.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.17-20 Evaluation metrics; pp.23-25 prompts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; Human behavior/outcome measure; HCI/perception construct scale; Theory-specific rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The study measures real participant mood/affect change and emotional relief, although not in a clinical patient sample.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.17-20 User study/Evaluation metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated affect scale and participant mood change make this the closest real therapeutic-outcome measure; human check recommended for consequence label.</t>
   </si>
   <si>
     <t>Berrezueta-Guzman2024Future</t>
   </si>
   <si>
-    <t>Future of ADHD Care: Evaluating the Efficacy of ChatGPT in Therapy Enhancement</t>
+    <t xml:space="preserve">Future of ADHD Care: Evaluating the Efficacy of ChatGPT in Therapy Enhancement</t>
   </si>
   <si>
     <t>./papers/104.pdf</t>
   </si>
   <si>
-    <t>CBT; music therapy; ADHD interventions; theory of mind</t>
-  </si>
-  <si>
-    <t>CBT and other ADHD-related therapies appear in background, but do not clearly shape the study design or evaluation.</t>
-  </si>
-  <si>
-    <t>pp.1, 3-4</t>
-  </si>
-  <si>
-    <t>No theory-specific evaluation criteria found in checked sections.</t>
-  </si>
-  <si>
-    <t>None / not evident</t>
-  </si>
-  <si>
-    <t>Theory is background-only in the available evidence.</t>
+    <t xml:space="preserve">CBT; music therapy; ADHD interventions; theory of mind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT and other ADHD-related therapies appear in background, but do not clearly shape the study design or evaluation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 3-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No theory-specific evaluation criteria found in checked sections.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None / not evident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory is background-only in the available evidence.</t>
   </si>
   <si>
     <t>Low</t>
@@ -1718,386 +1713,362 @@
     <t>Na2024CBT-LLM</t>
   </si>
   <si>
-    <t>CBT-LLM: A Chinese Large Language Model for Cognitive Behavioral Therapy-based Mental Health Question Answering</t>
+    <t xml:space="preserve">CBT-LLM: A Chinese Large Language Model for Cognitive Behavioral Therapy-based Mental Health Question Answering</t>
   </si>
   <si>
     <t>./papers/106.pdf</t>
   </si>
   <si>
-    <t>CBT; CBT principles; CBT structured intervention strategies; psychological health Q&amp;A</t>
-  </si>
-  <si>
-    <t>CBT principles shape prompts, dataset construction, and structured intervention responses.</t>
-  </si>
-  <si>
-    <t>pp.1, 7</t>
-  </si>
-  <si>
-    <t>CBT; CBT structured intervention strategies; CBT-based psychotherapy response quality</t>
-  </si>
-  <si>
-    <t>Human evaluation assesses quality of responses generated based on CBT in psychotherapy counseling, with CBT structured intervention tasks.</t>
-  </si>
-  <si>
-    <t>p.7 Human Evaluation</t>
-  </si>
-  <si>
-    <t>No downstream human or clinical outcome is measured.</t>
-  </si>
-  <si>
-    <t>CBT task/rubric defines evaluation.</t>
+    <t xml:space="preserve">CBT; CBT principles; CBT structured intervention strategies; psychological health Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT principles shape prompts, dataset construction, and structured intervention responses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.1, 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT; CBT structured intervention strategies; CBT-based psychotherapy response quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human evaluation assesses quality of responses generated based on CBT in psychotherapy counseling, with CBT structured intervention tasks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.7 Human Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream human or clinical outcome is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT task/rubric defines evaluation.</t>
   </si>
   <si>
     <t>Sharma2023Cognitive</t>
   </si>
   <si>
-    <t>Cognitive Reframing of Negative Thoughts through Human-Language Model Interaction</t>
+    <t xml:space="preserve">Cognitive Reframing of Negative Thoughts through Human-Language Model Interaction</t>
   </si>
   <si>
     <t>./papers/107.pdf</t>
   </si>
   <si>
-    <t>cognitive reframing; empathy communication mechanisms; cognitive distortion/negative thoughts</t>
-  </si>
-  <si>
-    <t>The task centers on cognitive reframing of negative thoughts and uses a psychologically grounded empathy framework.</t>
-  </si>
-  <si>
-    <t>pp.5, 7</t>
-  </si>
-  <si>
-    <t>cognitive reframing; empathy mechanisms; emotional reactions; interpretations; explorations; relatability; helpfulness</t>
-  </si>
-  <si>
-    <t>Evaluation uses an empathy model with manually labeled reframed thoughts and human ratings of reframing relatability/helpfulness.</t>
-  </si>
-  <si>
-    <t>pp.5, 7 Evaluation</t>
-  </si>
-  <si>
-    <t>Ratings address outputs, not actual human behavior or symptom change.</t>
-  </si>
-  <si>
-    <t>Cognitive reframing and empathy constructs define evaluation dimensions.</t>
+    <t xml:space="preserve">cognitive reframing; empathy communication mechanisms; cognitive distortion/negative thoughts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The task centers on cognitive reframing of negative thoughts and uses a psychologically grounded empathy framework.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.5, 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cognitive reframing; empathy mechanisms; emotional reactions; interpretations; explorations; relatability; helpfulness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation uses an empathy model with manually labeled reframed thoughts and human ratings of reframing relatability/helpfulness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.5, 7 Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratings address outputs, not actual human behavior or symptom change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognitive reframing and empathy constructs define evaluation dimensions.</t>
   </si>
   <si>
     <t>Kang2024Can</t>
   </si>
   <si>
-    <t>Can Large Language Models be Good Emotional Supporter? Mitigating Preference Bias on Emotional Support Conversation</t>
+    <t xml:space="preserve">Can Large Language Models be Good Emotional Supporter? Mitigating Preference Bias on Emotional Support Conversation</t>
   </si>
   <si>
     <t>./papers/108.pdf</t>
   </si>
   <si>
-    <t>emotional support strategies; exploration; comforting; action; strategy-response alignment</t>
-  </si>
-  <si>
-    <t>The paper uses emotional-support strategy constructs, but broader theory grounding is informal.</t>
-  </si>
-  <si>
-    <t>pp.3, 8</t>
-  </si>
-  <si>
-    <t>emotional support strategies; exploration; comforting; action; strategy-response alignment; response quality rubric</t>
-  </si>
-  <si>
-    <t>Human evaluation samples by strategy and rates strategy-response alignment and quality using rubrics.</t>
-  </si>
-  <si>
-    <t>p.8 Human Evaluation</t>
-  </si>
-  <si>
-    <t>No user support outcome, behavior change, or deployment consequence is measured.</t>
-  </si>
-  <si>
-    <t>Emotional-support strategy labels and alignment criteria define evaluation, even though grounding is partial.</t>
+    <t xml:space="preserve">emotional support strategies; exploration; comforting; action; strategy-response alignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The paper uses emotional-support strategy constructs, but broader theory grounding is informal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.3, 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional support strategies; exploration; comforting; action; strategy-response alignment; response quality rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human evaluation samples by strategy and rates strategy-response alignment and quality using rubrics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.8 Human Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No user support outcome, behavior change, or deployment consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emotional-support strategy labels and alignment criteria define evaluation, even though grounding is partial.</t>
   </si>
   <si>
     <t>Chen2023LLM-empowered</t>
   </si>
   <si>
-    <t>LLM-empowered Chatbots for Psychiatrist and Patient Simulation: Application and Evaluation</t>
+    <t xml:space="preserve">LLM-empowered Chatbots for Psychiatrist and Patient Simulation: Application and Evaluation</t>
   </si>
   <si>
     <t>./papers/109.pdf</t>
   </si>
   <si>
-    <t>PHQ-9; Beck depression severity; depression symptoms; psychiatrist objectives</t>
-  </si>
-  <si>
-    <t>Clinical depression and symptom constructs shape psychiatrist/patient chatbot objectives and metrics, but grounding is practitioner/domain-driven rather than a full theory framework.</t>
-  </si>
-  <si>
-    <t>pp.2, 11</t>
-  </si>
-  <si>
-    <t>depression severity; diagnosis accuracy; symptom recall; PHQ-9; Beck Depression Inventory</t>
-  </si>
-  <si>
-    <t>Evaluation metrics include diagnosis accuracy for depression severity and symptom recall for the doctor chatbot.</t>
-  </si>
-  <si>
-    <t>p.11 Appendix D Evaluation Metrics</t>
-  </si>
-  <si>
-    <t>Clinical diagnostic benchmark; Theory-specific benchmark/task</t>
-  </si>
-  <si>
-    <t>No real patient outcome or deployment consequence is measured.</t>
-  </si>
-  <si>
-    <t>Clinical diagnostic/symptom constructs define evaluation, despite partial grounding.</t>
+    <t xml:space="preserve">PHQ-9; Beck depression severity; depression symptoms; psychiatrist objectives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical depression and symptom constructs shape psychiatrist/patient chatbot objectives and metrics, but grounding is practitioner/domain-driven rather than a full theory framework.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depression severity; diagnosis accuracy; symptom recall; PHQ-9; Beck Depression Inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation metrics include diagnosis accuracy for depression severity and symptom recall for the doctor chatbot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.11 Appendix D Evaluation Metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical diagnostic benchmark; Theory-specific benchmark/task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No real patient outcome or deployment consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical diagnostic/symptom constructs define evaluation, despite partial grounding.</t>
   </si>
   <si>
     <t>Schmidgall2025AgentClinic</t>
   </si>
   <si>
-    <t>AgentClinic: a multimodal agent benchmark to evaluate AI in simulated clinical environments</t>
+    <t xml:space="preserve">AgentClinic: a multimodal agent benchmark to evaluate AI in simulated clinical environments</t>
   </si>
   <si>
     <t>./papers/110.pdf</t>
   </si>
   <si>
-    <t>clinical diagnostic reasoning; diagnostic accuracy; doctor empathy; patient realism</t>
-  </si>
-  <si>
-    <t>AgentClinic is clinically/domain grounded in simulated diagnostic environments, but not strongly grounded in counseling/therapy theory.</t>
-  </si>
-  <si>
-    <t>pp.24, 37</t>
-  </si>
-  <si>
-    <t>diagnostic accuracy; doctor empathy; patient realism; clinical assessment</t>
-  </si>
-  <si>
-    <t>Evaluation includes diagnostic accuracy and generic 1-10 ratings for doctor empathy/realism; theory-specific psychiatric/counseling constructs are limited.</t>
-  </si>
-  <si>
-    <t>pp.24, 37 Evaluation prompts/experiments</t>
-  </si>
-  <si>
-    <t>Clinical diagnostic benchmark; Custom expert rating</t>
-  </si>
-  <si>
-    <t>No downstream patient or deployment consequence is measured.</t>
-  </si>
-  <si>
-    <t>Clinical evaluation is present but broad/generic relative to therapy theory.</t>
+    <t xml:space="preserve">clinical diagnostic reasoning; diagnostic accuracy; doctor empathy; patient realism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgentClinic is clinically/domain grounded in simulated diagnostic environments, but not strongly grounded in counseling/therapy theory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.24, 37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diagnostic accuracy; doctor empathy; patient realism; clinical assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluation includes diagnostic accuracy and generic 1-10 ratings for doctor empathy/realism; theory-specific psychiatric/counseling constructs are limited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.24, 37 Evaluation prompts/experiments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical diagnostic benchmark; Custom expert rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No downstream patient or deployment consequence is measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical evaluation is present but broad/generic relative to therapy theory.</t>
   </si>
   <si>
     <t>Wang2025Psychological</t>
   </si>
   <si>
-    <t>Psychological Counseling CanNot Be Achieved Overnight: Automated Psychological Counseling Through Multi-Session Conversations</t>
+    <t xml:space="preserve">Psychological Counseling CanNot Be Achieved Overnight: Automated Psychological Counseling Through Multi-Session Conversations</t>
   </si>
   <si>
     <t>./papers/111.pdf</t>
   </si>
   <si>
-    <t>CBT; working alliance; WAI-SR; multi-session counseling; psychological metrics</t>
-  </si>
-  <si>
-    <t>CBT motivates multi-session counseling data/model design, and working alliance is used as a consistent evaluation construct.</t>
-  </si>
-  <si>
-    <t>pp.2, 5, 10</t>
-  </si>
-  <si>
-    <t>CBT; working alliance; WAI-SR; counselor-client working alliance; psychological metrics</t>
-  </si>
-  <si>
-    <t>Dataset quality evaluation uses psychology experts/GPT-4o and includes counselor-client working alliance as a consistent measure across datasets.</t>
-  </si>
-  <si>
-    <t>p.5 Dataset Quality Evaluations; p.10 WAI-SR reference</t>
-  </si>
-  <si>
-    <t>Validated scale; Theory-specific rubric; LLM judge with theory-specific criteria; Custom expert rating</t>
-  </si>
-  <si>
-    <t>Working alliance is evaluated for generated/multi-session counseling examples rather than measured real-client outcomes.</t>
-  </si>
-  <si>
-    <t>p.5 Evaluation</t>
-  </si>
-  <si>
-    <t>Working alliance/CBT define evaluation of multi-session counseling quality.</t>
+    <t xml:space="preserve">CBT; working alliance; WAI-SR; multi-session counseling; psychological metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT motivates multi-session counseling data/model design, and working alliance is used as a consistent evaluation construct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.2, 5, 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBT; working alliance; WAI-SR; counselor-client working alliance; psychological metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dataset quality evaluation uses psychology experts/GPT-4o and includes counselor-client working alliance as a consistent measure across datasets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5 Dataset Quality Evaluations; p.10 WAI-SR reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validated scale; Theory-specific rubric; LLM judge with theory-specific criteria; Custom expert rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working alliance is evaluated for generated/multi-session counseling examples rather than measured real-client outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.5 Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working alliance/CBT define evaluation of multi-session counseling quality.</t>
   </si>
   <si>
     <t>Tanana2019Development</t>
   </si>
   <si>
-    <t>Development and Evaluation of ClientBot: Patient-Like Conversational Agent to Train Basic Counseling Skills</t>
+    <t xml:space="preserve">Development and Evaluation of ClientBot: Patient-Like Conversational Agent to Train Basic Counseling Skills</t>
   </si>
   <si>
     <t>./papers/112.pdf</t>
   </si>
   <si>
-    <t>motivational interviewing; MISC; active listening; counseling microskills; open questions; reflections</t>
-  </si>
-  <si>
-    <t>ClientBot trains basic counseling skills using MI-based active-listening skill codes.</t>
-  </si>
-  <si>
-    <t>MISC; motivational interviewing; open questions; closed questions; reflections; counseling skill acquisition</t>
-  </si>
-  <si>
-    <t>Feedback classifies trainee responses into MI-based counseling skills using MISC-derived labels; evaluation measures open-question and reflection use in treatment vs control groups.</t>
-  </si>
-  <si>
-    <t>pp.6-10 Evaluation/Results</t>
-  </si>
-  <si>
-    <t>Established therapy/counseling coding system; Human behavior/outcome measure; Theory-specific benchmark/task</t>
-  </si>
-  <si>
-    <t>The study measures trainee skill use and retention of open questions/reflections after training.</t>
-  </si>
-  <si>
-    <t>pp.7-10 Results/Discussion</t>
-  </si>
-  <si>
-    <t>MI/MISC codes define feedback and measured human skill acquisition.</t>
+    <t xml:space="preserve">motivational interviewing; MISC; active listening; counseling microskills; open questions; reflections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClientBot trains basic counseling skills using MI-based active-listening skill codes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISC; motivational interviewing; open questions; closed questions; reflections; counseling skill acquisition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback classifies trainee responses into MI-based counseling skills using MISC-derived labels; evaluation measures open-question and reflection use in treatment vs control groups.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.6-10 Evaluation/Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Established therapy/counseling coding system; Human behavior/outcome measure; Theory-specific benchmark/task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The study measures trainee skill use and retention of open questions/reflections after training.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pp.7-10 Results/Discussion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI/MISC codes define feedback and measured human skill acquisition.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="17">
     <font>
-      <sz val="12"/>
+      <sz val="12.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="12.000000"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="12.000000"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.000000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.000000"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12.000000"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.000000"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.000000"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.000000"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18.000000"/>
       <color theme="3"/>
       <name val="Aptos Display"/>
-      <family val="2"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="12.000000"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="12.000000"/>
+      <color indexed="2"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2110,22 +2081,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
     <fill>
@@ -2140,188 +2234,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor indexed="47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor indexed="26"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor indexed="5"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="10">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -2336,7 +2279,73 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -2351,153 +2360,114 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="9" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="10" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="11" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="12" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="13" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="14" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="15" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="16" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="17" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="18" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="19" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="20" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="21" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="22" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="23" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="24" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="25" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="2" fillId="26" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="3" fillId="27" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
+    <xf fontId="4" fillId="28" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf fontId="6" fillId="29" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="7" fillId="0" borderId="3" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0"/>
+    <xf fontId="8" fillId="0" borderId="4" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0"/>
+    <xf fontId="9" fillId="0" borderId="5" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0"/>
+    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf fontId="10" fillId="30" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
+    <xf fontId="11" fillId="0" borderId="6" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0"/>
+    <xf fontId="12" fillId="31" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="32" borderId="7" numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1" applyProtection="0"/>
+    <xf fontId="13" fillId="27" borderId="8" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
+    <xf fontId="14" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf fontId="15" fillId="0" borderId="9" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0"/>
+    <xf fontId="16" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
+    <cellStyle name="20% - Accent2" xfId="2" builtinId="34"/>
+    <cellStyle name="20% - Accent3" xfId="3" builtinId="38"/>
+    <cellStyle name="20% - Accent4" xfId="4" builtinId="42"/>
+    <cellStyle name="20% - Accent5" xfId="5" builtinId="46"/>
+    <cellStyle name="20% - Accent6" xfId="6" builtinId="50"/>
+    <cellStyle name="40% - Accent1" xfId="7" builtinId="31"/>
+    <cellStyle name="40% - Accent2" xfId="8" builtinId="35"/>
+    <cellStyle name="40% - Accent3" xfId="9" builtinId="39"/>
+    <cellStyle name="40% - Accent4" xfId="10" builtinId="43"/>
+    <cellStyle name="40% - Accent5" xfId="11" builtinId="47"/>
+    <cellStyle name="40% - Accent6" xfId="12" builtinId="51"/>
+    <cellStyle name="60% - Accent1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - Accent2" xfId="14" builtinId="36"/>
+    <cellStyle name="60% - Accent3" xfId="15" builtinId="40"/>
+    <cellStyle name="60% - Accent4" xfId="16" builtinId="44"/>
+    <cellStyle name="60% - Accent5" xfId="17" builtinId="48"/>
+    <cellStyle name="60% - Accent6" xfId="18" builtinId="52"/>
+    <cellStyle name="Accent1" xfId="19" builtinId="29"/>
+    <cellStyle name="Accent2" xfId="20" builtinId="33"/>
+    <cellStyle name="Accent3" xfId="21" builtinId="37"/>
+    <cellStyle name="Accent4" xfId="22" builtinId="41"/>
+    <cellStyle name="Accent5" xfId="23" builtinId="45"/>
+    <cellStyle name="Accent6" xfId="24" builtinId="49"/>
+    <cellStyle name="Bad" xfId="25" builtinId="27"/>
+    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="27" builtinId="23"/>
+    <cellStyle name="Explanatory Text" xfId="28" builtinId="53"/>
+    <cellStyle name="Good" xfId="29" builtinId="26"/>
+    <cellStyle name="Heading 1" xfId="30" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="31" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="32" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="33" builtinId="19"/>
+    <cellStyle name="Input" xfId="34" builtinId="20"/>
+    <cellStyle name="Linked Cell" xfId="35" builtinId="24"/>
+    <cellStyle name="Neutral" xfId="36" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="37" builtinId="10"/>
+    <cellStyle name="Output" xfId="38" builtinId="21"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Total" xfId="40" builtinId="25"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2512,12 +2482,291 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2559,108 +2808,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Display"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2668,7 +2823,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2694,7 +2849,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2771,7 +2926,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2803,7 +2958,7 @@
   </a:themeElements>
   <a:objectDefaults>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -2822,21 +2977,37 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB696ED2-4C83-B44E-BAB8-C7B77309F98C}">
-  <dimension ref="A1:U53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="8.3359375"/>
+    <col bestFit="1" min="2" max="2" width="28.10546875"/>
+    <col bestFit="1" min="3" max="3" width="129.6640625"/>
+    <col bestFit="1" min="4" max="4" width="13.4453125"/>
+    <col bestFit="1" min="5" max="5" width="15.6640625"/>
+    <col bestFit="1" min="6" max="6" width="100.21484375"/>
+    <col bestFit="1" min="7" max="7" width="142.21484375"/>
+    <col bestFit="1" min="8" max="8" width="30.6640625"/>
+    <col bestFit="1" min="9" max="9" width="31.77734375"/>
+    <col bestFit="1" min="10" max="10" width="94.99609375"/>
+    <col bestFit="1" min="11" max="11" width="181.77734375"/>
+    <col bestFit="1" min="12" max="12" width="44.6640625"/>
+    <col bestFit="1" min="13" max="13" width="111.6640625"/>
+    <col bestFit="1" min="14" max="14" width="28.3359375"/>
+    <col bestFit="1" min="15" max="15" width="120.21484375"/>
+    <col bestFit="1" min="16" max="16" width="32.21484375"/>
+    <col bestFit="1" min="17" max="17" width="126.77734375"/>
+    <col bestFit="1" min="18" max="18" width="9.88671875"/>
+    <col bestFit="1" min="19" max="19" width="19.99609375"/>
+    <col bestFit="1" min="20" max="20" width="123.77734375"/>
+    <col bestFit="1" min="21" max="21" width="55.3359375"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2901,7 +3072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" ht="15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2966,7 +3137,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
         <v>6</v>
       </c>
@@ -3031,7 +3202,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4">
         <v>10</v>
       </c>
@@ -3096,7 +3267,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5">
         <v>13</v>
       </c>
@@ -3161,7 +3332,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6">
         <v>15</v>
       </c>
@@ -3226,7 +3397,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7">
         <v>18</v>
       </c>
@@ -3291,7 +3462,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8">
         <v>21</v>
       </c>
@@ -3356,7 +3527,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9">
         <v>23</v>
       </c>
@@ -3421,7 +3592,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10">
         <v>29</v>
       </c>
@@ -3486,7 +3657,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11">
         <v>31</v>
       </c>
@@ -3551,7 +3722,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12">
         <v>34</v>
       </c>
@@ -3616,7 +3787,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13">
         <v>38</v>
       </c>
@@ -3681,7 +3852,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14">
         <v>39</v>
       </c>
@@ -3746,7 +3917,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15">
         <v>45</v>
       </c>
@@ -3811,7 +3982,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16">
         <v>47</v>
       </c>
@@ -3876,7 +4047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17">
         <v>49</v>
       </c>
@@ -3941,7 +4112,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18">
         <v>56</v>
       </c>
@@ -4006,7 +4177,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19">
         <v>58</v>
       </c>
@@ -4071,7 +4242,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20">
         <v>60</v>
       </c>
@@ -4136,7 +4307,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21">
         <v>63</v>
       </c>
@@ -4201,7 +4372,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22">
         <v>65</v>
       </c>
@@ -4266,7 +4437,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23">
         <v>68</v>
       </c>
@@ -4331,7 +4502,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24">
         <v>69</v>
       </c>
@@ -4396,7 +4567,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25">
         <v>71</v>
       </c>
@@ -4461,7 +4632,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26">
         <v>72</v>
       </c>
@@ -4526,7 +4697,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27">
         <v>75</v>
       </c>
@@ -4591,7 +4762,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28">
         <v>77</v>
       </c>
@@ -4656,7 +4827,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29">
         <v>80</v>
       </c>
@@ -4721,7 +4892,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30">
         <v>81</v>
       </c>
@@ -4786,7 +4957,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31">
         <v>83</v>
       </c>
@@ -4851,7 +5022,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32">
         <v>84</v>
       </c>
@@ -4916,7 +5087,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33">
         <v>86</v>
       </c>
@@ -4981,7 +5152,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34">
         <v>87</v>
       </c>
@@ -5046,7 +5217,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35">
         <v>89</v>
       </c>
@@ -5111,7 +5282,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36">
         <v>91</v>
       </c>
@@ -5176,7 +5347,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" ht="18" customHeight="1">
       <c r="A37">
         <v>92</v>
       </c>
@@ -5241,7 +5412,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38">
         <v>93</v>
       </c>
@@ -5306,7 +5477,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39">
         <v>94</v>
       </c>
@@ -5371,7 +5542,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40">
         <v>95</v>
       </c>
@@ -5436,7 +5607,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41">
         <v>97</v>
       </c>
@@ -5501,7 +5672,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42">
         <v>99</v>
       </c>
@@ -5566,7 +5737,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43">
         <v>100</v>
       </c>
@@ -5631,7 +5802,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44">
         <v>101</v>
       </c>
@@ -5696,7 +5867,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45">
         <v>102</v>
       </c>
@@ -5761,7 +5932,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46">
         <v>104</v>
       </c>
@@ -5826,7 +5997,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47">
         <v>106</v>
       </c>
@@ -5891,7 +6062,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48">
         <v>107</v>
       </c>
@@ -5956,7 +6127,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49">
         <v>108</v>
       </c>
@@ -6021,7 +6192,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50">
         <v>109</v>
       </c>
@@ -6086,7 +6257,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51">
         <v>110</v>
       </c>
@@ -6151,7 +6322,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" ht="17" customHeight="1">
       <c r="A52">
         <v>111</v>
       </c>
@@ -6216,7 +6387,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53">
         <v>112</v>
       </c>
@@ -6282,6 +6453,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>